--- a/codelists/statins_raw.xlsx
+++ b/codelists/statins_raw.xlsx
@@ -410,7 +410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM179"/>
+  <dimension ref="A1:AW180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.48" customWidth="1" min="1" max="1"/>
@@ -452,6 +452,16 @@
     <col width="11.96" customWidth="1" min="37" max="37"/>
     <col width="12.88" customWidth="1" min="38" max="38"/>
     <col width="11.96" customWidth="1" min="39" max="39"/>
+    <col width="12.88" customWidth="1" min="40" max="40"/>
+    <col width="17.48" customWidth="1" min="41" max="41"/>
+    <col width="11.04" customWidth="1" min="42" max="42"/>
+    <col width="11.04" customWidth="1" min="43" max="43"/>
+    <col width="11.04" customWidth="1" min="44" max="44"/>
+    <col width="10.12" customWidth="1" min="45" max="45"/>
+    <col width="11.04" customWidth="1" min="46" max="46"/>
+    <col width="11.04" customWidth="1" min="47" max="47"/>
+    <col width="23" customWidth="1" min="48" max="48"/>
+    <col width="25.76" customWidth="1" min="49" max="49"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -650,6 +660,56 @@
           <t>simvastatin</t>
         </is>
       </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>statin_count</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>external_codelist</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>lshtm_2102</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>lshtm_2199</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>lshtm_2470</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>hdruk_972</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>hdruk_1013</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>hdruk_1600</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>oc_openpresc_allstatins</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>oc_openpresc_lowmedstatins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -781,6 +841,26 @@
       <c r="AM2" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AN2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS2" s="1" t="n"/>
+      <c r="AT2" s="1" t="n"/>
+      <c r="AU2" s="1" t="n"/>
+      <c r="AV2" s="1" t="n"/>
+      <c r="AW2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -912,6 +992,26 @@
       <c r="AM3" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AN3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS3" s="1" t="n"/>
+      <c r="AT3" s="1" t="n"/>
+      <c r="AU3" s="1" t="n"/>
+      <c r="AV3" s="1" t="n"/>
+      <c r="AW3" s="1" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1055,6 +1155,34 @@
       <c r="AM4" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW4" s="1" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1198,6 +1326,34 @@
       <c r="AM5" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW5" s="1" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1340,6 +1496,36 @@
       </c>
       <c r="AM6" s="1" t="n">
         <v>0</v>
+      </c>
+      <c r="AN6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW6" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1472,6 +1658,26 @@
       <c r="AM7" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AN7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS7" s="1" t="n"/>
+      <c r="AT7" s="1" t="n"/>
+      <c r="AU7" s="1" t="n"/>
+      <c r="AV7" s="1" t="n"/>
+      <c r="AW7" s="1" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1615,6 +1821,34 @@
       <c r="AM8" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW8" s="1" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1746,6 +1980,18 @@
       <c r="AM9" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO9" s="1" t="n"/>
+      <c r="AP9" s="1" t="n"/>
+      <c r="AQ9" s="1" t="n"/>
+      <c r="AR9" s="1" t="n"/>
+      <c r="AS9" s="1" t="n"/>
+      <c r="AT9" s="1" t="n"/>
+      <c r="AU9" s="1" t="n"/>
+      <c r="AV9" s="1" t="n"/>
+      <c r="AW9" s="1" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1877,6 +2123,26 @@
       <c r="AM10" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS10" s="1" t="n"/>
+      <c r="AT10" s="1" t="n"/>
+      <c r="AU10" s="1" t="n"/>
+      <c r="AV10" s="1" t="n"/>
+      <c r="AW10" s="1" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2008,6 +2274,26 @@
       <c r="AM11" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS11" s="1" t="n"/>
+      <c r="AT11" s="1" t="n"/>
+      <c r="AU11" s="1" t="n"/>
+      <c r="AV11" s="1" t="n"/>
+      <c r="AW11" s="1" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2139,6 +2425,26 @@
       <c r="AM12" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS12" s="1" t="n"/>
+      <c r="AT12" s="1" t="n"/>
+      <c r="AU12" s="1" t="n"/>
+      <c r="AV12" s="1" t="n"/>
+      <c r="AW12" s="1" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2270,6 +2576,26 @@
       <c r="AM13" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS13" s="1" t="n"/>
+      <c r="AT13" s="1" t="n"/>
+      <c r="AU13" s="1" t="n"/>
+      <c r="AV13" s="1" t="n"/>
+      <c r="AW13" s="1" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2413,6 +2739,26 @@
       <c r="AM14" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP14" s="1" t="n"/>
+      <c r="AQ14" s="1" t="n"/>
+      <c r="AR14" s="1" t="n"/>
+      <c r="AS14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV14" s="1" t="n"/>
+      <c r="AW14" s="1" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2544,6 +2890,26 @@
       <c r="AM15" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS15" s="1" t="n"/>
+      <c r="AT15" s="1" t="n"/>
+      <c r="AU15" s="1" t="n"/>
+      <c r="AV15" s="1" t="n"/>
+      <c r="AW15" s="1" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2675,6 +3041,26 @@
       <c r="AM16" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AN16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS16" s="1" t="n"/>
+      <c r="AT16" s="1" t="n"/>
+      <c r="AU16" s="1" t="n"/>
+      <c r="AV16" s="1" t="n"/>
+      <c r="AW16" s="1" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2806,6 +3192,26 @@
       <c r="AM17" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS17" s="1" t="n"/>
+      <c r="AT17" s="1" t="n"/>
+      <c r="AU17" s="1" t="n"/>
+      <c r="AV17" s="1" t="n"/>
+      <c r="AW17" s="1" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2937,6 +3343,18 @@
       <c r="AM18" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO18" s="1" t="n"/>
+      <c r="AP18" s="1" t="n"/>
+      <c r="AQ18" s="1" t="n"/>
+      <c r="AR18" s="1" t="n"/>
+      <c r="AS18" s="1" t="n"/>
+      <c r="AT18" s="1" t="n"/>
+      <c r="AU18" s="1" t="n"/>
+      <c r="AV18" s="1" t="n"/>
+      <c r="AW18" s="1" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3054,7 +3472,7 @@
         <v>0</v>
       </c>
       <c r="AE19" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF19" s="1" t="n">
         <v>0</v>
@@ -3080,6 +3498,26 @@
       <c r="AM19" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP19" s="1" t="n"/>
+      <c r="AQ19" s="1" t="n"/>
+      <c r="AR19" s="1" t="n"/>
+      <c r="AS19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV19" s="1" t="n"/>
+      <c r="AW19" s="1" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3223,6 +3661,36 @@
       <c r="AM20" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AN20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW20" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3366,6 +3834,36 @@
       <c r="AM21" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW21" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3508,6 +4006,36 @@
       </c>
       <c r="AM22" s="1" t="n">
         <v>0</v>
+      </c>
+      <c r="AN22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW22" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -3640,6 +4168,18 @@
       <c r="AM23" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO23" s="1" t="n"/>
+      <c r="AP23" s="1" t="n"/>
+      <c r="AQ23" s="1" t="n"/>
+      <c r="AR23" s="1" t="n"/>
+      <c r="AS23" s="1" t="n"/>
+      <c r="AT23" s="1" t="n"/>
+      <c r="AU23" s="1" t="n"/>
+      <c r="AV23" s="1" t="n"/>
+      <c r="AW23" s="1" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3783,6 +4323,26 @@
       <c r="AM24" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP24" s="1" t="n"/>
+      <c r="AQ24" s="1" t="n"/>
+      <c r="AR24" s="1" t="n"/>
+      <c r="AS24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV24" s="1" t="n"/>
+      <c r="AW24" s="1" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3924,6 +4484,36 @@
         <v>0</v>
       </c>
       <c r="AM25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW25" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4057,6 +4647,18 @@
       <c r="AM26" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN26" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO26" s="1" t="n"/>
+      <c r="AP26" s="1" t="n"/>
+      <c r="AQ26" s="1" t="n"/>
+      <c r="AR26" s="1" t="n"/>
+      <c r="AS26" s="1" t="n"/>
+      <c r="AT26" s="1" t="n"/>
+      <c r="AU26" s="1" t="n"/>
+      <c r="AV26" s="1" t="n"/>
+      <c r="AW26" s="1" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4188,6 +4790,18 @@
       <c r="AM27" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO27" s="1" t="n"/>
+      <c r="AP27" s="1" t="n"/>
+      <c r="AQ27" s="1" t="n"/>
+      <c r="AR27" s="1" t="n"/>
+      <c r="AS27" s="1" t="n"/>
+      <c r="AT27" s="1" t="n"/>
+      <c r="AU27" s="1" t="n"/>
+      <c r="AV27" s="1" t="n"/>
+      <c r="AW27" s="1" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4305,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="AE28" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF28" s="1" t="n">
         <v>0</v>
@@ -4331,6 +4945,26 @@
       <c r="AM28" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP28" s="1" t="n"/>
+      <c r="AQ28" s="1" t="n"/>
+      <c r="AR28" s="1" t="n"/>
+      <c r="AS28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV28" s="1" t="n"/>
+      <c r="AW28" s="1" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4462,6 +5096,18 @@
       <c r="AM29" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN29" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO29" s="1" t="n"/>
+      <c r="AP29" s="1" t="n"/>
+      <c r="AQ29" s="1" t="n"/>
+      <c r="AR29" s="1" t="n"/>
+      <c r="AS29" s="1" t="n"/>
+      <c r="AT29" s="1" t="n"/>
+      <c r="AU29" s="1" t="n"/>
+      <c r="AV29" s="1" t="n"/>
+      <c r="AW29" s="1" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4593,6 +5239,26 @@
       <c r="AM30" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN30" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO30" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP30" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ30" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR30" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS30" s="1" t="n"/>
+      <c r="AT30" s="1" t="n"/>
+      <c r="AU30" s="1" t="n"/>
+      <c r="AV30" s="1" t="n"/>
+      <c r="AW30" s="1" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4724,6 +5390,18 @@
       <c r="AM31" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN31" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO31" s="1" t="n"/>
+      <c r="AP31" s="1" t="n"/>
+      <c r="AQ31" s="1" t="n"/>
+      <c r="AR31" s="1" t="n"/>
+      <c r="AS31" s="1" t="n"/>
+      <c r="AT31" s="1" t="n"/>
+      <c r="AU31" s="1" t="n"/>
+      <c r="AV31" s="1" t="n"/>
+      <c r="AW31" s="1" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4867,6 +5545,26 @@
       <c r="AM32" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN32" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO32" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP32" s="1" t="n"/>
+      <c r="AQ32" s="1" t="n"/>
+      <c r="AR32" s="1" t="n"/>
+      <c r="AS32" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT32" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU32" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV32" s="1" t="n"/>
+      <c r="AW32" s="1" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5008,6 +5706,36 @@
         <v>0</v>
       </c>
       <c r="AM33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW33" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5141,6 +5869,26 @@
       <c r="AM34" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN34" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO34" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP34" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ34" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR34" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS34" s="1" t="n"/>
+      <c r="AT34" s="1" t="n"/>
+      <c r="AU34" s="1" t="n"/>
+      <c r="AV34" s="1" t="n"/>
+      <c r="AW34" s="1" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5283,6 +6031,36 @@
       </c>
       <c r="AM35" s="1" t="n">
         <v>0</v>
+      </c>
+      <c r="AN35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW35" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -5415,6 +6193,18 @@
       <c r="AM36" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN36" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO36" s="1" t="n"/>
+      <c r="AP36" s="1" t="n"/>
+      <c r="AQ36" s="1" t="n"/>
+      <c r="AR36" s="1" t="n"/>
+      <c r="AS36" s="1" t="n"/>
+      <c r="AT36" s="1" t="n"/>
+      <c r="AU36" s="1" t="n"/>
+      <c r="AV36" s="1" t="n"/>
+      <c r="AW36" s="1" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5558,6 +6348,36 @@
       <c r="AM37" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN37" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO37" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP37" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ37" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR37" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS37" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT37" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU37" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV37" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW37" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5701,6 +6521,34 @@
       <c r="AM38" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW38" s="1" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5832,6 +6680,18 @@
       <c r="AM39" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN39" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO39" s="1" t="n"/>
+      <c r="AP39" s="1" t="n"/>
+      <c r="AQ39" s="1" t="n"/>
+      <c r="AR39" s="1" t="n"/>
+      <c r="AS39" s="1" t="n"/>
+      <c r="AT39" s="1" t="n"/>
+      <c r="AU39" s="1" t="n"/>
+      <c r="AV39" s="1" t="n"/>
+      <c r="AW39" s="1" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5975,6 +6835,26 @@
       <c r="AM40" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN40" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO40" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP40" s="1" t="n"/>
+      <c r="AQ40" s="1" t="n"/>
+      <c r="AR40" s="1" t="n"/>
+      <c r="AS40" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT40" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU40" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV40" s="1" t="n"/>
+      <c r="AW40" s="1" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6118,6 +6998,26 @@
       <c r="AM41" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN41" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO41" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP41" s="1" t="n"/>
+      <c r="AQ41" s="1" t="n"/>
+      <c r="AR41" s="1" t="n"/>
+      <c r="AS41" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT41" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU41" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV41" s="1" t="n"/>
+      <c r="AW41" s="1" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6261,6 +7161,26 @@
       <c r="AM42" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN42" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO42" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP42" s="1" t="n"/>
+      <c r="AQ42" s="1" t="n"/>
+      <c r="AR42" s="1" t="n"/>
+      <c r="AS42" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT42" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU42" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV42" s="1" t="n"/>
+      <c r="AW42" s="1" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6392,6 +7312,26 @@
       <c r="AM43" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AN43" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO43" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP43" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ43" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR43" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS43" s="1" t="n"/>
+      <c r="AT43" s="1" t="n"/>
+      <c r="AU43" s="1" t="n"/>
+      <c r="AV43" s="1" t="n"/>
+      <c r="AW43" s="1" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6535,6 +7475,26 @@
       <c r="AM44" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN44" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO44" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP44" s="1" t="n"/>
+      <c r="AQ44" s="1" t="n"/>
+      <c r="AR44" s="1" t="n"/>
+      <c r="AS44" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT44" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU44" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV44" s="1" t="n"/>
+      <c r="AW44" s="1" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6678,6 +7638,36 @@
       <c r="AM45" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AN45" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO45" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP45" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ45" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR45" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS45" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT45" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU45" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV45" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW45" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6795,7 +7785,7 @@
         <v>0</v>
       </c>
       <c r="AE46" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF46" s="1" t="n">
         <v>0</v>
@@ -6821,6 +7811,26 @@
       <c r="AM46" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN46" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO46" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP46" s="1" t="n"/>
+      <c r="AQ46" s="1" t="n"/>
+      <c r="AR46" s="1" t="n"/>
+      <c r="AS46" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT46" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU46" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV46" s="1" t="n"/>
+      <c r="AW46" s="1" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6964,6 +7974,26 @@
       <c r="AM47" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN47" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO47" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP47" s="1" t="n"/>
+      <c r="AQ47" s="1" t="n"/>
+      <c r="AR47" s="1" t="n"/>
+      <c r="AS47" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT47" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU47" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV47" s="1" t="n"/>
+      <c r="AW47" s="1" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -7107,6 +8137,26 @@
       <c r="AM48" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN48" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO48" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP48" s="1" t="n"/>
+      <c r="AQ48" s="1" t="n"/>
+      <c r="AR48" s="1" t="n"/>
+      <c r="AS48" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT48" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU48" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV48" s="1" t="n"/>
+      <c r="AW48" s="1" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -7238,6 +8288,18 @@
       <c r="AM49" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN49" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO49" s="1" t="n"/>
+      <c r="AP49" s="1" t="n"/>
+      <c r="AQ49" s="1" t="n"/>
+      <c r="AR49" s="1" t="n"/>
+      <c r="AS49" s="1" t="n"/>
+      <c r="AT49" s="1" t="n"/>
+      <c r="AU49" s="1" t="n"/>
+      <c r="AV49" s="1" t="n"/>
+      <c r="AW49" s="1" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -7369,6 +8431,26 @@
       <c r="AM50" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN50" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO50" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP50" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ50" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR50" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS50" s="1" t="n"/>
+      <c r="AT50" s="1" t="n"/>
+      <c r="AU50" s="1" t="n"/>
+      <c r="AV50" s="1" t="n"/>
+      <c r="AW50" s="1" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7512,6 +8594,34 @@
       <c r="AM51" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN51" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO51" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP51" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ51" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR51" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS51" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT51" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU51" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV51" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW51" s="1" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -7655,6 +8765,34 @@
       <c r="AM52" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN52" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO52" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP52" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ52" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR52" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS52" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT52" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU52" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV52" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW52" s="1" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7798,6 +8936,36 @@
       <c r="AM53" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AN53" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO53" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP53" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ53" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR53" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS53" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT53" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU53" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV53" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW53" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7940,6 +9108,32 @@
       </c>
       <c r="AM54" s="1" t="n">
         <v>0</v>
+      </c>
+      <c r="AN54" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO54" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP54" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ54" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR54" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS54" s="1" t="n"/>
+      <c r="AT54" s="1" t="n"/>
+      <c r="AU54" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV54" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW54" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -8072,6 +9266,26 @@
       <c r="AM55" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AN55" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO55" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP55" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ55" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR55" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS55" s="1" t="n"/>
+      <c r="AT55" s="1" t="n"/>
+      <c r="AU55" s="1" t="n"/>
+      <c r="AV55" s="1" t="n"/>
+      <c r="AW55" s="1" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -8215,6 +9429,36 @@
       <c r="AM56" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN56" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO56" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP56" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ56" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR56" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS56" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT56" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU56" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV56" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW56" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -8358,6 +9602,26 @@
       <c r="AM57" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN57" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO57" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP57" s="1" t="n"/>
+      <c r="AQ57" s="1" t="n"/>
+      <c r="AR57" s="1" t="n"/>
+      <c r="AS57" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT57" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU57" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV57" s="1" t="n"/>
+      <c r="AW57" s="1" t="n"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -8489,6 +9753,18 @@
       <c r="AM58" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN58" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO58" s="1" t="n"/>
+      <c r="AP58" s="1" t="n"/>
+      <c r="AQ58" s="1" t="n"/>
+      <c r="AR58" s="1" t="n"/>
+      <c r="AS58" s="1" t="n"/>
+      <c r="AT58" s="1" t="n"/>
+      <c r="AU58" s="1" t="n"/>
+      <c r="AV58" s="1" t="n"/>
+      <c r="AW58" s="1" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -8620,6 +9896,26 @@
       <c r="AM59" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN59" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO59" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP59" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ59" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR59" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS59" s="1" t="n"/>
+      <c r="AT59" s="1" t="n"/>
+      <c r="AU59" s="1" t="n"/>
+      <c r="AV59" s="1" t="n"/>
+      <c r="AW59" s="1" t="n"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -8747,6 +10043,18 @@
       <c r="AM60" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN60" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO60" s="1" t="n"/>
+      <c r="AP60" s="1" t="n"/>
+      <c r="AQ60" s="1" t="n"/>
+      <c r="AR60" s="1" t="n"/>
+      <c r="AS60" s="1" t="n"/>
+      <c r="AT60" s="1" t="n"/>
+      <c r="AU60" s="1" t="n"/>
+      <c r="AV60" s="1" t="n"/>
+      <c r="AW60" s="1" t="n"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -8890,6 +10198,26 @@
       <c r="AM61" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN61" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO61" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP61" s="1" t="n"/>
+      <c r="AQ61" s="1" t="n"/>
+      <c r="AR61" s="1" t="n"/>
+      <c r="AS61" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT61" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU61" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV61" s="1" t="n"/>
+      <c r="AW61" s="1" t="n"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -9033,6 +10361,36 @@
       <c r="AM62" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN62" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO62" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP62" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ62" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR62" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS62" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT62" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU62" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV62" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW62" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -9176,6 +10534,34 @@
       <c r="AM63" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN63" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO63" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP63" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ63" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR63" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS63" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT63" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU63" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV63" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW63" s="1" t="n"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -9307,6 +10693,18 @@
       <c r="AM64" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN64" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO64" s="1" t="n"/>
+      <c r="AP64" s="1" t="n"/>
+      <c r="AQ64" s="1" t="n"/>
+      <c r="AR64" s="1" t="n"/>
+      <c r="AS64" s="1" t="n"/>
+      <c r="AT64" s="1" t="n"/>
+      <c r="AU64" s="1" t="n"/>
+      <c r="AV64" s="1" t="n"/>
+      <c r="AW64" s="1" t="n"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -9438,6 +10836,26 @@
       <c r="AM65" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN65" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO65" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP65" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ65" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR65" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS65" s="1" t="n"/>
+      <c r="AT65" s="1" t="n"/>
+      <c r="AU65" s="1" t="n"/>
+      <c r="AV65" s="1" t="n"/>
+      <c r="AW65" s="1" t="n"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -9581,6 +10999,26 @@
       <c r="AM66" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN66" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO66" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP66" s="1" t="n"/>
+      <c r="AQ66" s="1" t="n"/>
+      <c r="AR66" s="1" t="n"/>
+      <c r="AS66" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT66" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU66" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV66" s="1" t="n"/>
+      <c r="AW66" s="1" t="n"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -9712,6 +11150,26 @@
       <c r="AM67" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AN67" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO67" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP67" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ67" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR67" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS67" s="1" t="n"/>
+      <c r="AT67" s="1" t="n"/>
+      <c r="AU67" s="1" t="n"/>
+      <c r="AV67" s="1" t="n"/>
+      <c r="AW67" s="1" t="n"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -9855,6 +11313,36 @@
       <c r="AM68" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN68" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO68" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP68" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ68" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR68" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS68" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT68" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU68" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV68" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW68" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -9998,6 +11486,36 @@
       <c r="AM69" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AN69" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO69" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP69" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ69" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR69" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS69" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT69" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU69" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV69" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW69" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -10141,6 +11659,36 @@
       <c r="AM70" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN70" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO70" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP70" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ70" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR70" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS70" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT70" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU70" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV70" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW70" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -10284,6 +11832,26 @@
       <c r="AM71" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN71" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO71" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP71" s="1" t="n"/>
+      <c r="AQ71" s="1" t="n"/>
+      <c r="AR71" s="1" t="n"/>
+      <c r="AS71" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT71" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU71" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV71" s="1" t="n"/>
+      <c r="AW71" s="1" t="n"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -10427,6 +11995,34 @@
       <c r="AM72" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN72" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO72" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP72" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ72" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR72" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS72" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT72" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU72" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV72" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW72" s="1" t="n"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -10570,6 +12166,28 @@
       <c r="AM73" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN73" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO73" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP73" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ73" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR73" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS73" s="1" t="n"/>
+      <c r="AT73" s="1" t="n"/>
+      <c r="AU73" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV73" s="1" t="n"/>
+      <c r="AW73" s="1" t="n"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -10713,6 +12331,34 @@
       <c r="AM74" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN74" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO74" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP74" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ74" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR74" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS74" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT74" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU74" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV74" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW74" s="1" t="n"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -10855,6 +12501,36 @@
       </c>
       <c r="AM75" s="1" t="n">
         <v>0</v>
+      </c>
+      <c r="AN75" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO75" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP75" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ75" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR75" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS75" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT75" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU75" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV75" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW75" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -10959,6 +12635,18 @@
       <c r="AM76" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN76" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO76" s="1" t="n"/>
+      <c r="AP76" s="1" t="n"/>
+      <c r="AQ76" s="1" t="n"/>
+      <c r="AR76" s="1" t="n"/>
+      <c r="AS76" s="1" t="n"/>
+      <c r="AT76" s="1" t="n"/>
+      <c r="AU76" s="1" t="n"/>
+      <c r="AV76" s="1" t="n"/>
+      <c r="AW76" s="1" t="n"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -11102,6 +12790,32 @@
       <c r="AM77" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AN77" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO77" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP77" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ77" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR77" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS77" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT77" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU77" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV77" s="1" t="n"/>
+      <c r="AW77" s="1" t="n"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -11245,6 +12959,32 @@
       <c r="AM78" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AN78" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO78" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP78" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ78" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR78" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS78" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT78" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU78" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV78" s="1" t="n"/>
+      <c r="AW78" s="1" t="n"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -11388,6 +13128,36 @@
       <c r="AM79" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN79" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO79" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP79" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ79" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR79" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS79" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT79" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU79" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV79" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW79" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -11531,6 +13301,34 @@
       <c r="AM80" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN80" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO80" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP80" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ80" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR80" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS80" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT80" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU80" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV80" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW80" s="1" t="n"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -11648,7 +13446,7 @@
         <v>0</v>
       </c>
       <c r="AE81" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF81" s="1" t="n">
         <v>0</v>
@@ -11674,6 +13472,26 @@
       <c r="AM81" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN81" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO81" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP81" s="1" t="n"/>
+      <c r="AQ81" s="1" t="n"/>
+      <c r="AR81" s="1" t="n"/>
+      <c r="AS81" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT81" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU81" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV81" s="1" t="n"/>
+      <c r="AW81" s="1" t="n"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -11755,7 +13573,7 @@
         <v>0</v>
       </c>
       <c r="AE82" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF82" s="1" t="n">
         <v>0</v>
@@ -11781,6 +13599,18 @@
       <c r="AM82" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN82" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO82" s="1" t="n"/>
+      <c r="AP82" s="1" t="n"/>
+      <c r="AQ82" s="1" t="n"/>
+      <c r="AR82" s="1" t="n"/>
+      <c r="AS82" s="1" t="n"/>
+      <c r="AT82" s="1" t="n"/>
+      <c r="AU82" s="1" t="n"/>
+      <c r="AV82" s="1" t="n"/>
+      <c r="AW82" s="1" t="n"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -11924,6 +13754,26 @@
       <c r="AM83" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN83" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO83" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP83" s="1" t="n"/>
+      <c r="AQ83" s="1" t="n"/>
+      <c r="AR83" s="1" t="n"/>
+      <c r="AS83" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT83" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU83" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV83" s="1" t="n"/>
+      <c r="AW83" s="1" t="n"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -12067,6 +13917,26 @@
       <c r="AM84" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN84" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO84" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP84" s="1" t="n"/>
+      <c r="AQ84" s="1" t="n"/>
+      <c r="AR84" s="1" t="n"/>
+      <c r="AS84" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT84" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU84" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV84" s="1" t="n"/>
+      <c r="AW84" s="1" t="n"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -12210,6 +14080,26 @@
       <c r="AM85" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN85" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO85" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP85" s="1" t="n"/>
+      <c r="AQ85" s="1" t="n"/>
+      <c r="AR85" s="1" t="n"/>
+      <c r="AS85" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT85" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU85" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV85" s="1" t="n"/>
+      <c r="AW85" s="1" t="n"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -12353,6 +14243,36 @@
       <c r="AM86" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN86" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO86" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP86" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ86" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR86" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS86" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT86" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU86" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV86" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW86" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -12496,6 +14416,28 @@
       <c r="AM87" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AN87" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO87" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP87" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ87" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR87" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS87" s="1" t="n"/>
+      <c r="AT87" s="1" t="n"/>
+      <c r="AU87" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV87" s="1" t="n"/>
+      <c r="AW87" s="1" t="n"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -12599,6 +14541,18 @@
       <c r="AM88" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN88" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO88" s="1" t="n"/>
+      <c r="AP88" s="1" t="n"/>
+      <c r="AQ88" s="1" t="n"/>
+      <c r="AR88" s="1" t="n"/>
+      <c r="AS88" s="1" t="n"/>
+      <c r="AT88" s="1" t="n"/>
+      <c r="AU88" s="1" t="n"/>
+      <c r="AV88" s="1" t="n"/>
+      <c r="AW88" s="1" t="n"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -12716,7 +14670,7 @@
         <v>0</v>
       </c>
       <c r="AE89" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF89" s="1" t="n">
         <v>0</v>
@@ -12742,6 +14696,22 @@
       <c r="AM89" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN89" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO89" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP89" s="1" t="n"/>
+      <c r="AQ89" s="1" t="n"/>
+      <c r="AR89" s="1" t="n"/>
+      <c r="AS89" s="1" t="n"/>
+      <c r="AT89" s="1" t="n"/>
+      <c r="AU89" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV89" s="1" t="n"/>
+      <c r="AW89" s="1" t="n"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -12885,6 +14855,26 @@
       <c r="AM90" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN90" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO90" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP90" s="1" t="n"/>
+      <c r="AQ90" s="1" t="n"/>
+      <c r="AR90" s="1" t="n"/>
+      <c r="AS90" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT90" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU90" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV90" s="1" t="n"/>
+      <c r="AW90" s="1" t="n"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -13028,6 +15018,22 @@
       <c r="AM91" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN91" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO91" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP91" s="1" t="n"/>
+      <c r="AQ91" s="1" t="n"/>
+      <c r="AR91" s="1" t="n"/>
+      <c r="AS91" s="1" t="n"/>
+      <c r="AT91" s="1" t="n"/>
+      <c r="AU91" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV91" s="1" t="n"/>
+      <c r="AW91" s="1" t="n"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -13171,6 +15177,26 @@
       <c r="AM92" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN92" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO92" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP92" s="1" t="n"/>
+      <c r="AQ92" s="1" t="n"/>
+      <c r="AR92" s="1" t="n"/>
+      <c r="AS92" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT92" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU92" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV92" s="1" t="n"/>
+      <c r="AW92" s="1" t="n"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -13314,6 +15340,26 @@
       <c r="AM93" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN93" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO93" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP93" s="1" t="n"/>
+      <c r="AQ93" s="1" t="n"/>
+      <c r="AR93" s="1" t="n"/>
+      <c r="AS93" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT93" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU93" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV93" s="1" t="n"/>
+      <c r="AW93" s="1" t="n"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -13457,6 +15503,22 @@
       <c r="AM94" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN94" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO94" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP94" s="1" t="n"/>
+      <c r="AQ94" s="1" t="n"/>
+      <c r="AR94" s="1" t="n"/>
+      <c r="AS94" s="1" t="n"/>
+      <c r="AT94" s="1" t="n"/>
+      <c r="AU94" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV94" s="1" t="n"/>
+      <c r="AW94" s="1" t="n"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -13600,6 +15662,22 @@
       <c r="AM95" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN95" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO95" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP95" s="1" t="n"/>
+      <c r="AQ95" s="1" t="n"/>
+      <c r="AR95" s="1" t="n"/>
+      <c r="AS95" s="1" t="n"/>
+      <c r="AT95" s="1" t="n"/>
+      <c r="AU95" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV95" s="1" t="n"/>
+      <c r="AW95" s="1" t="n"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -13743,6 +15821,36 @@
       <c r="AM96" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AN96" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO96" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP96" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ96" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR96" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS96" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT96" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU96" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV96" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW96" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -13884,6 +15992,36 @@
         <v>0</v>
       </c>
       <c r="AM97" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN97" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO97" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP97" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ97" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR97" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS97" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT97" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU97" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV97" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW97" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13993,6 +16131,18 @@
       <c r="AM98" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN98" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO98" s="1" t="n"/>
+      <c r="AP98" s="1" t="n"/>
+      <c r="AQ98" s="1" t="n"/>
+      <c r="AR98" s="1" t="n"/>
+      <c r="AS98" s="1" t="n"/>
+      <c r="AT98" s="1" t="n"/>
+      <c r="AU98" s="1" t="n"/>
+      <c r="AV98" s="1" t="n"/>
+      <c r="AW98" s="1" t="n"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -14136,6 +16286,24 @@
       <c r="AM99" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN99" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO99" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP99" s="1" t="n"/>
+      <c r="AQ99" s="1" t="n"/>
+      <c r="AR99" s="1" t="n"/>
+      <c r="AS99" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT99" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU99" s="1" t="n"/>
+      <c r="AV99" s="1" t="n"/>
+      <c r="AW99" s="1" t="n"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -14279,6 +16447,28 @@
       <c r="AM100" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN100" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO100" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP100" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ100" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR100" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS100" s="1" t="n"/>
+      <c r="AT100" s="1" t="n"/>
+      <c r="AU100" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV100" s="1" t="n"/>
+      <c r="AW100" s="1" t="n"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -14382,6 +16572,18 @@
       <c r="AM101" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN101" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO101" s="1" t="n"/>
+      <c r="AP101" s="1" t="n"/>
+      <c r="AQ101" s="1" t="n"/>
+      <c r="AR101" s="1" t="n"/>
+      <c r="AS101" s="1" t="n"/>
+      <c r="AT101" s="1" t="n"/>
+      <c r="AU101" s="1" t="n"/>
+      <c r="AV101" s="1" t="n"/>
+      <c r="AW101" s="1" t="n"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -14525,6 +16727,28 @@
       <c r="AM102" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AN102" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO102" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP102" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ102" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR102" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS102" s="1" t="n"/>
+      <c r="AT102" s="1" t="n"/>
+      <c r="AU102" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV102" s="1" t="n"/>
+      <c r="AW102" s="1" t="n"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -14668,6 +16892,36 @@
       <c r="AM103" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN103" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO103" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP103" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ103" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR103" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS103" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT103" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU103" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV103" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW103" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -14811,6 +17065,26 @@
       <c r="AM104" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN104" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO104" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP104" s="1" t="n"/>
+      <c r="AQ104" s="1" t="n"/>
+      <c r="AR104" s="1" t="n"/>
+      <c r="AS104" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT104" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU104" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV104" s="1" t="n"/>
+      <c r="AW104" s="1" t="n"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -14954,6 +17228,22 @@
       <c r="AM105" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN105" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO105" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP105" s="1" t="n"/>
+      <c r="AQ105" s="1" t="n"/>
+      <c r="AR105" s="1" t="n"/>
+      <c r="AS105" s="1" t="n"/>
+      <c r="AT105" s="1" t="n"/>
+      <c r="AU105" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV105" s="1" t="n"/>
+      <c r="AW105" s="1" t="n"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -15097,6 +17387,22 @@
       <c r="AM106" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN106" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO106" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP106" s="1" t="n"/>
+      <c r="AQ106" s="1" t="n"/>
+      <c r="AR106" s="1" t="n"/>
+      <c r="AS106" s="1" t="n"/>
+      <c r="AT106" s="1" t="n"/>
+      <c r="AU106" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV106" s="1" t="n"/>
+      <c r="AW106" s="1" t="n"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -15240,6 +17546,22 @@
       <c r="AM107" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN107" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO107" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP107" s="1" t="n"/>
+      <c r="AQ107" s="1" t="n"/>
+      <c r="AR107" s="1" t="n"/>
+      <c r="AS107" s="1" t="n"/>
+      <c r="AT107" s="1" t="n"/>
+      <c r="AU107" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV107" s="1" t="n"/>
+      <c r="AW107" s="1" t="n"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -15383,6 +17705,26 @@
       <c r="AM108" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN108" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO108" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP108" s="1" t="n"/>
+      <c r="AQ108" s="1" t="n"/>
+      <c r="AR108" s="1" t="n"/>
+      <c r="AS108" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT108" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU108" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV108" s="1" t="n"/>
+      <c r="AW108" s="1" t="n"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -15526,6 +17868,22 @@
       <c r="AM109" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN109" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO109" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP109" s="1" t="n"/>
+      <c r="AQ109" s="1" t="n"/>
+      <c r="AR109" s="1" t="n"/>
+      <c r="AS109" s="1" t="n"/>
+      <c r="AT109" s="1" t="n"/>
+      <c r="AU109" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV109" s="1" t="n"/>
+      <c r="AW109" s="1" t="n"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -15669,6 +18027,32 @@
       <c r="AM110" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN110" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO110" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP110" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ110" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR110" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS110" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT110" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU110" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV110" s="1" t="n"/>
+      <c r="AW110" s="1" t="n"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -15812,6 +18196,34 @@
       <c r="AM111" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AN111" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO111" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP111" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ111" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR111" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS111" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT111" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU111" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV111" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW111" s="1" t="n"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -15929,7 +18341,7 @@
         <v>0</v>
       </c>
       <c r="AE112" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF112" s="1" t="n">
         <v>0</v>
@@ -15955,6 +18367,26 @@
       <c r="AM112" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN112" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO112" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP112" s="1" t="n"/>
+      <c r="AQ112" s="1" t="n"/>
+      <c r="AR112" s="1" t="n"/>
+      <c r="AS112" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT112" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU112" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV112" s="1" t="n"/>
+      <c r="AW112" s="1" t="n"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -16098,6 +18530,34 @@
       <c r="AM113" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN113" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO113" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP113" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ113" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR113" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS113" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT113" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU113" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV113" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW113" s="1" t="n"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -16241,6 +18701,34 @@
       <c r="AM114" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AN114" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO114" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP114" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ114" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR114" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS114" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT114" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU114" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV114" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW114" s="1" t="n"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -16384,6 +18872,28 @@
       <c r="AM115" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN115" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO115" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP115" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ115" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR115" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS115" s="1" t="n"/>
+      <c r="AT115" s="1" t="n"/>
+      <c r="AU115" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV115" s="1" t="n"/>
+      <c r="AW115" s="1" t="n"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -16487,6 +18997,18 @@
       <c r="AM116" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN116" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO116" s="1" t="n"/>
+      <c r="AP116" s="1" t="n"/>
+      <c r="AQ116" s="1" t="n"/>
+      <c r="AR116" s="1" t="n"/>
+      <c r="AS116" s="1" t="n"/>
+      <c r="AT116" s="1" t="n"/>
+      <c r="AU116" s="1" t="n"/>
+      <c r="AV116" s="1" t="n"/>
+      <c r="AW116" s="1" t="n"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -16630,6 +19152,36 @@
       <c r="AM117" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN117" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO117" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP117" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ117" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR117" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS117" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT117" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU117" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV117" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW117" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -16773,6 +19325,36 @@
       <c r="AM118" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN118" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO118" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP118" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ118" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR118" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS118" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT118" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU118" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV118" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW118" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -16916,6 +19498,26 @@
       <c r="AM119" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN119" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO119" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP119" s="1" t="n"/>
+      <c r="AQ119" s="1" t="n"/>
+      <c r="AR119" s="1" t="n"/>
+      <c r="AS119" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT119" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU119" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV119" s="1" t="n"/>
+      <c r="AW119" s="1" t="n"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -17059,6 +19661,18 @@
       <c r="AM120" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN120" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO120" s="1" t="n"/>
+      <c r="AP120" s="1" t="n"/>
+      <c r="AQ120" s="1" t="n"/>
+      <c r="AR120" s="1" t="n"/>
+      <c r="AS120" s="1" t="n"/>
+      <c r="AT120" s="1" t="n"/>
+      <c r="AU120" s="1" t="n"/>
+      <c r="AV120" s="1" t="n"/>
+      <c r="AW120" s="1" t="n"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -17202,6 +19816,18 @@
       <c r="AM121" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN121" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO121" s="1" t="n"/>
+      <c r="AP121" s="1" t="n"/>
+      <c r="AQ121" s="1" t="n"/>
+      <c r="AR121" s="1" t="n"/>
+      <c r="AS121" s="1" t="n"/>
+      <c r="AT121" s="1" t="n"/>
+      <c r="AU121" s="1" t="n"/>
+      <c r="AV121" s="1" t="n"/>
+      <c r="AW121" s="1" t="n"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -17345,6 +19971,18 @@
       <c r="AM122" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN122" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO122" s="1" t="n"/>
+      <c r="AP122" s="1" t="n"/>
+      <c r="AQ122" s="1" t="n"/>
+      <c r="AR122" s="1" t="n"/>
+      <c r="AS122" s="1" t="n"/>
+      <c r="AT122" s="1" t="n"/>
+      <c r="AU122" s="1" t="n"/>
+      <c r="AV122" s="1" t="n"/>
+      <c r="AW122" s="1" t="n"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -17488,6 +20126,26 @@
       <c r="AM123" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN123" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO123" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP123" s="1" t="n"/>
+      <c r="AQ123" s="1" t="n"/>
+      <c r="AR123" s="1" t="n"/>
+      <c r="AS123" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT123" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU123" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV123" s="1" t="n"/>
+      <c r="AW123" s="1" t="n"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -17631,6 +20289,34 @@
       <c r="AM124" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AN124" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO124" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP124" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ124" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR124" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS124" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT124" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU124" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV124" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW124" s="1" t="n"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -17734,6 +20420,18 @@
       <c r="AM125" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN125" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO125" s="1" t="n"/>
+      <c r="AP125" s="1" t="n"/>
+      <c r="AQ125" s="1" t="n"/>
+      <c r="AR125" s="1" t="n"/>
+      <c r="AS125" s="1" t="n"/>
+      <c r="AT125" s="1" t="n"/>
+      <c r="AU125" s="1" t="n"/>
+      <c r="AV125" s="1" t="n"/>
+      <c r="AW125" s="1" t="n"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -17877,6 +20575,32 @@
       <c r="AM126" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN126" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO126" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP126" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ126" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR126" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS126" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT126" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU126" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV126" s="1" t="n"/>
+      <c r="AW126" s="1" t="n"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -18020,6 +20744,26 @@
       <c r="AM127" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN127" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO127" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP127" s="1" t="n"/>
+      <c r="AQ127" s="1" t="n"/>
+      <c r="AR127" s="1" t="n"/>
+      <c r="AS127" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT127" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU127" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV127" s="1" t="n"/>
+      <c r="AW127" s="1" t="n"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -18137,7 +20881,7 @@
         <v>0</v>
       </c>
       <c r="AE128" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF128" s="1" t="n">
         <v>0</v>
@@ -18163,6 +20907,22 @@
       <c r="AM128" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN128" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO128" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP128" s="1" t="n"/>
+      <c r="AQ128" s="1" t="n"/>
+      <c r="AR128" s="1" t="n"/>
+      <c r="AS128" s="1" t="n"/>
+      <c r="AT128" s="1" t="n"/>
+      <c r="AU128" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV128" s="1" t="n"/>
+      <c r="AW128" s="1" t="n"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -18306,6 +21066,18 @@
       <c r="AM129" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN129" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO129" s="1" t="n"/>
+      <c r="AP129" s="1" t="n"/>
+      <c r="AQ129" s="1" t="n"/>
+      <c r="AR129" s="1" t="n"/>
+      <c r="AS129" s="1" t="n"/>
+      <c r="AT129" s="1" t="n"/>
+      <c r="AU129" s="1" t="n"/>
+      <c r="AV129" s="1" t="n"/>
+      <c r="AW129" s="1" t="n"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -18449,6 +21221,18 @@
       <c r="AM130" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN130" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO130" s="1" t="n"/>
+      <c r="AP130" s="1" t="n"/>
+      <c r="AQ130" s="1" t="n"/>
+      <c r="AR130" s="1" t="n"/>
+      <c r="AS130" s="1" t="n"/>
+      <c r="AT130" s="1" t="n"/>
+      <c r="AU130" s="1" t="n"/>
+      <c r="AV130" s="1" t="n"/>
+      <c r="AW130" s="1" t="n"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -18592,6 +21376,28 @@
       <c r="AM131" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN131" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO131" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP131" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ131" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR131" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS131" s="1" t="n"/>
+      <c r="AT131" s="1" t="n"/>
+      <c r="AU131" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV131" s="1" t="n"/>
+      <c r="AW131" s="1" t="n"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -18735,6 +21541,32 @@
       <c r="AM132" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN132" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO132" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP132" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ132" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR132" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS132" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT132" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU132" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV132" s="1" t="n"/>
+      <c r="AW132" s="1" t="n"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -18852,7 +21684,7 @@
         <v>0</v>
       </c>
       <c r="AE133" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF133" s="1" t="n">
         <v>0</v>
@@ -18878,6 +21710,26 @@
       <c r="AM133" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN133" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO133" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP133" s="1" t="n"/>
+      <c r="AQ133" s="1" t="n"/>
+      <c r="AR133" s="1" t="n"/>
+      <c r="AS133" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT133" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU133" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV133" s="1" t="n"/>
+      <c r="AW133" s="1" t="n"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -19021,6 +21873,26 @@
       <c r="AM134" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN134" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO134" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP134" s="1" t="n"/>
+      <c r="AQ134" s="1" t="n"/>
+      <c r="AR134" s="1" t="n"/>
+      <c r="AS134" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT134" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU134" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV134" s="1" t="n"/>
+      <c r="AW134" s="1" t="n"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -19164,6 +22036,22 @@
       <c r="AM135" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN135" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO135" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP135" s="1" t="n"/>
+      <c r="AQ135" s="1" t="n"/>
+      <c r="AR135" s="1" t="n"/>
+      <c r="AS135" s="1" t="n"/>
+      <c r="AT135" s="1" t="n"/>
+      <c r="AU135" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV135" s="1" t="n"/>
+      <c r="AW135" s="1" t="n"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -19307,6 +22195,26 @@
       <c r="AM136" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN136" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO136" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP136" s="1" t="n"/>
+      <c r="AQ136" s="1" t="n"/>
+      <c r="AR136" s="1" t="n"/>
+      <c r="AS136" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT136" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU136" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV136" s="1" t="n"/>
+      <c r="AW136" s="1" t="n"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -19450,6 +22358,26 @@
       <c r="AM137" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN137" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO137" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP137" s="1" t="n"/>
+      <c r="AQ137" s="1" t="n"/>
+      <c r="AR137" s="1" t="n"/>
+      <c r="AS137" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT137" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU137" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV137" s="1" t="n"/>
+      <c r="AW137" s="1" t="n"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -19593,6 +22521,26 @@
       <c r="AM138" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN138" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO138" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP138" s="1" t="n"/>
+      <c r="AQ138" s="1" t="n"/>
+      <c r="AR138" s="1" t="n"/>
+      <c r="AS138" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT138" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU138" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV138" s="1" t="n"/>
+      <c r="AW138" s="1" t="n"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -19736,6 +22684,18 @@
       <c r="AM139" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN139" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO139" s="1" t="n"/>
+      <c r="AP139" s="1" t="n"/>
+      <c r="AQ139" s="1" t="n"/>
+      <c r="AR139" s="1" t="n"/>
+      <c r="AS139" s="1" t="n"/>
+      <c r="AT139" s="1" t="n"/>
+      <c r="AU139" s="1" t="n"/>
+      <c r="AV139" s="1" t="n"/>
+      <c r="AW139" s="1" t="n"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -19839,6 +22799,18 @@
       <c r="AM140" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN140" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO140" s="1" t="n"/>
+      <c r="AP140" s="1" t="n"/>
+      <c r="AQ140" s="1" t="n"/>
+      <c r="AR140" s="1" t="n"/>
+      <c r="AS140" s="1" t="n"/>
+      <c r="AT140" s="1" t="n"/>
+      <c r="AU140" s="1" t="n"/>
+      <c r="AV140" s="1" t="n"/>
+      <c r="AW140" s="1" t="n"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -19982,6 +22954,26 @@
       <c r="AM141" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN141" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO141" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP141" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ141" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR141" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS141" s="1" t="n"/>
+      <c r="AT141" s="1" t="n"/>
+      <c r="AU141" s="1" t="n"/>
+      <c r="AV141" s="1" t="n"/>
+      <c r="AW141" s="1" t="n"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -20125,6 +23117,32 @@
       <c r="AM142" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN142" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO142" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP142" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ142" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR142" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS142" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT142" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU142" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV142" s="1" t="n"/>
+      <c r="AW142" s="1" t="n"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -20268,6 +23286,26 @@
       <c r="AM143" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN143" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO143" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP143" s="1" t="n"/>
+      <c r="AQ143" s="1" t="n"/>
+      <c r="AR143" s="1" t="n"/>
+      <c r="AS143" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT143" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU143" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV143" s="1" t="n"/>
+      <c r="AW143" s="1" t="n"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -20411,6 +23449,26 @@
       <c r="AM144" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN144" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO144" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP144" s="1" t="n"/>
+      <c r="AQ144" s="1" t="n"/>
+      <c r="AR144" s="1" t="n"/>
+      <c r="AS144" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT144" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU144" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV144" s="1" t="n"/>
+      <c r="AW144" s="1" t="n"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -20554,6 +23612,26 @@
       <c r="AM145" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN145" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO145" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP145" s="1" t="n"/>
+      <c r="AQ145" s="1" t="n"/>
+      <c r="AR145" s="1" t="n"/>
+      <c r="AS145" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT145" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU145" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV145" s="1" t="n"/>
+      <c r="AW145" s="1" t="n"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -20697,6 +23775,32 @@
       <c r="AM146" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AN146" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO146" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP146" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ146" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR146" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS146" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT146" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU146" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV146" s="1" t="n"/>
+      <c r="AW146" s="1" t="n"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -20840,6 +23944,18 @@
       <c r="AM147" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN147" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO147" s="1" t="n"/>
+      <c r="AP147" s="1" t="n"/>
+      <c r="AQ147" s="1" t="n"/>
+      <c r="AR147" s="1" t="n"/>
+      <c r="AS147" s="1" t="n"/>
+      <c r="AT147" s="1" t="n"/>
+      <c r="AU147" s="1" t="n"/>
+      <c r="AV147" s="1" t="n"/>
+      <c r="AW147" s="1" t="n"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -20983,6 +24099,18 @@
       <c r="AM148" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN148" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO148" s="1" t="n"/>
+      <c r="AP148" s="1" t="n"/>
+      <c r="AQ148" s="1" t="n"/>
+      <c r="AR148" s="1" t="n"/>
+      <c r="AS148" s="1" t="n"/>
+      <c r="AT148" s="1" t="n"/>
+      <c r="AU148" s="1" t="n"/>
+      <c r="AV148" s="1" t="n"/>
+      <c r="AW148" s="1" t="n"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -21114,6 +24242,26 @@
       <c r="AM149" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN149" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO149" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP149" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ149" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR149" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS149" s="1" t="n"/>
+      <c r="AT149" s="1" t="n"/>
+      <c r="AU149" s="1" t="n"/>
+      <c r="AV149" s="1" t="n"/>
+      <c r="AW149" s="1" t="n"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -21257,6 +24405,28 @@
       <c r="AM150" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AN150" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO150" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP150" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ150" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR150" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS150" s="1" t="n"/>
+      <c r="AT150" s="1" t="n"/>
+      <c r="AU150" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV150" s="1" t="n"/>
+      <c r="AW150" s="1" t="n"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -21374,7 +24544,7 @@
         <v>0</v>
       </c>
       <c r="AE151" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF151" s="1" t="n">
         <v>0</v>
@@ -21400,6 +24570,26 @@
       <c r="AM151" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN151" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO151" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP151" s="1" t="n"/>
+      <c r="AQ151" s="1" t="n"/>
+      <c r="AR151" s="1" t="n"/>
+      <c r="AS151" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT151" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU151" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV151" s="1" t="n"/>
+      <c r="AW151" s="1" t="n"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -21543,6 +24733,18 @@
       <c r="AM152" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN152" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO152" s="1" t="n"/>
+      <c r="AP152" s="1" t="n"/>
+      <c r="AQ152" s="1" t="n"/>
+      <c r="AR152" s="1" t="n"/>
+      <c r="AS152" s="1" t="n"/>
+      <c r="AT152" s="1" t="n"/>
+      <c r="AU152" s="1" t="n"/>
+      <c r="AV152" s="1" t="n"/>
+      <c r="AW152" s="1" t="n"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -21686,6 +24888,18 @@
       <c r="AM153" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN153" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO153" s="1" t="n"/>
+      <c r="AP153" s="1" t="n"/>
+      <c r="AQ153" s="1" t="n"/>
+      <c r="AR153" s="1" t="n"/>
+      <c r="AS153" s="1" t="n"/>
+      <c r="AT153" s="1" t="n"/>
+      <c r="AU153" s="1" t="n"/>
+      <c r="AV153" s="1" t="n"/>
+      <c r="AW153" s="1" t="n"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -21829,6 +25043,32 @@
       <c r="AM154" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AN154" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO154" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP154" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ154" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR154" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS154" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT154" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU154" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV154" s="1" t="n"/>
+      <c r="AW154" s="1" t="n"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -21972,6 +25212,22 @@
       <c r="AM155" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN155" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO155" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP155" s="1" t="n"/>
+      <c r="AQ155" s="1" t="n"/>
+      <c r="AR155" s="1" t="n"/>
+      <c r="AS155" s="1" t="n"/>
+      <c r="AT155" s="1" t="n"/>
+      <c r="AU155" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV155" s="1" t="n"/>
+      <c r="AW155" s="1" t="n"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -22075,6 +25331,18 @@
       <c r="AM156" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN156" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO156" s="1" t="n"/>
+      <c r="AP156" s="1" t="n"/>
+      <c r="AQ156" s="1" t="n"/>
+      <c r="AR156" s="1" t="n"/>
+      <c r="AS156" s="1" t="n"/>
+      <c r="AT156" s="1" t="n"/>
+      <c r="AU156" s="1" t="n"/>
+      <c r="AV156" s="1" t="n"/>
+      <c r="AW156" s="1" t="n"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -22218,6 +25486,32 @@
       <c r="AM157" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN157" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO157" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP157" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ157" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR157" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS157" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT157" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU157" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV157" s="1" t="n"/>
+      <c r="AW157" s="1" t="n"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -22361,6 +25655,18 @@
       <c r="AM158" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN158" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO158" s="1" t="n"/>
+      <c r="AP158" s="1" t="n"/>
+      <c r="AQ158" s="1" t="n"/>
+      <c r="AR158" s="1" t="n"/>
+      <c r="AS158" s="1" t="n"/>
+      <c r="AT158" s="1" t="n"/>
+      <c r="AU158" s="1" t="n"/>
+      <c r="AV158" s="1" t="n"/>
+      <c r="AW158" s="1" t="n"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -22504,6 +25810,26 @@
       <c r="AM159" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN159" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO159" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP159" s="1" t="n"/>
+      <c r="AQ159" s="1" t="n"/>
+      <c r="AR159" s="1" t="n"/>
+      <c r="AS159" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT159" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU159" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV159" s="1" t="n"/>
+      <c r="AW159" s="1" t="n"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -22647,6 +25973,36 @@
       <c r="AM160" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN160" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO160" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP160" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ160" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR160" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS160" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT160" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU160" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV160" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW160" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -22790,6 +26146,32 @@
       <c r="AM161" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN161" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO161" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP161" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ161" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR161" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS161" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT161" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU161" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV161" s="1" t="n"/>
+      <c r="AW161" s="1" t="n"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -22933,6 +26315,18 @@
       <c r="AM162" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN162" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO162" s="1" t="n"/>
+      <c r="AP162" s="1" t="n"/>
+      <c r="AQ162" s="1" t="n"/>
+      <c r="AR162" s="1" t="n"/>
+      <c r="AS162" s="1" t="n"/>
+      <c r="AT162" s="1" t="n"/>
+      <c r="AU162" s="1" t="n"/>
+      <c r="AV162" s="1" t="n"/>
+      <c r="AW162" s="1" t="n"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -23076,6 +26470,32 @@
       <c r="AM163" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AN163" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO163" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP163" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ163" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR163" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS163" s="1" t="n"/>
+      <c r="AT163" s="1" t="n"/>
+      <c r="AU163" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV163" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW163" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -23219,6 +26639,22 @@
       <c r="AM164" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN164" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO164" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP164" s="1" t="n"/>
+      <c r="AQ164" s="1" t="n"/>
+      <c r="AR164" s="1" t="n"/>
+      <c r="AS164" s="1" t="n"/>
+      <c r="AT164" s="1" t="n"/>
+      <c r="AU164" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV164" s="1" t="n"/>
+      <c r="AW164" s="1" t="n"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -23362,6 +26798,26 @@
       <c r="AM165" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN165" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO165" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP165" s="1" t="n"/>
+      <c r="AQ165" s="1" t="n"/>
+      <c r="AR165" s="1" t="n"/>
+      <c r="AS165" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT165" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU165" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV165" s="1" t="n"/>
+      <c r="AW165" s="1" t="n"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -23493,6 +26949,18 @@
       <c r="AM166" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN166" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO166" s="1" t="n"/>
+      <c r="AP166" s="1" t="n"/>
+      <c r="AQ166" s="1" t="n"/>
+      <c r="AR166" s="1" t="n"/>
+      <c r="AS166" s="1" t="n"/>
+      <c r="AT166" s="1" t="n"/>
+      <c r="AU166" s="1" t="n"/>
+      <c r="AV166" s="1" t="n"/>
+      <c r="AW166" s="1" t="n"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -23636,6 +27104,36 @@
       <c r="AM167" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN167" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO167" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP167" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ167" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR167" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS167" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT167" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU167" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV167" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW167" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -23779,6 +27277,26 @@
       <c r="AM168" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AN168" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO168" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP168" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ168" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR168" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS168" s="1" t="n"/>
+      <c r="AT168" s="1" t="n"/>
+      <c r="AU168" s="1" t="n"/>
+      <c r="AV168" s="1" t="n"/>
+      <c r="AW168" s="1" t="n"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -23922,6 +27440,18 @@
       <c r="AM169" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN169" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO169" s="1" t="n"/>
+      <c r="AP169" s="1" t="n"/>
+      <c r="AQ169" s="1" t="n"/>
+      <c r="AR169" s="1" t="n"/>
+      <c r="AS169" s="1" t="n"/>
+      <c r="AT169" s="1" t="n"/>
+      <c r="AU169" s="1" t="n"/>
+      <c r="AV169" s="1" t="n"/>
+      <c r="AW169" s="1" t="n"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -24065,6 +27595,28 @@
       <c r="AM170" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AN170" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO170" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP170" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ170" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR170" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS170" s="1" t="n"/>
+      <c r="AT170" s="1" t="n"/>
+      <c r="AU170" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV170" s="1" t="n"/>
+      <c r="AW170" s="1" t="n"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -24208,6 +27760,32 @@
       <c r="AM171" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AN171" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO171" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP171" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ171" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR171" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS171" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT171" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU171" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV171" s="1" t="n"/>
+      <c r="AW171" s="1" t="n"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -24311,6 +27889,18 @@
       <c r="AM172" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN172" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO172" s="1" t="n"/>
+      <c r="AP172" s="1" t="n"/>
+      <c r="AQ172" s="1" t="n"/>
+      <c r="AR172" s="1" t="n"/>
+      <c r="AS172" s="1" t="n"/>
+      <c r="AT172" s="1" t="n"/>
+      <c r="AU172" s="1" t="n"/>
+      <c r="AV172" s="1" t="n"/>
+      <c r="AW172" s="1" t="n"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -24454,6 +28044,28 @@
       <c r="AM173" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AN173" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO173" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP173" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ173" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR173" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS173" s="1" t="n"/>
+      <c r="AT173" s="1" t="n"/>
+      <c r="AU173" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV173" s="1" t="n"/>
+      <c r="AW173" s="1" t="n"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -24597,6 +28209,22 @@
       <c r="AM174" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN174" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO174" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP174" s="1" t="n"/>
+      <c r="AQ174" s="1" t="n"/>
+      <c r="AR174" s="1" t="n"/>
+      <c r="AS174" s="1" t="n"/>
+      <c r="AT174" s="1" t="n"/>
+      <c r="AU174" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV174" s="1" t="n"/>
+      <c r="AW174" s="1" t="n"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -24740,6 +28368,22 @@
       <c r="AM175" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN175" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO175" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP175" s="1" t="n"/>
+      <c r="AQ175" s="1" t="n"/>
+      <c r="AR175" s="1" t="n"/>
+      <c r="AS175" s="1" t="n"/>
+      <c r="AT175" s="1" t="n"/>
+      <c r="AU175" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV175" s="1" t="n"/>
+      <c r="AW175" s="1" t="n"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -24883,6 +28527,28 @@
       <c r="AM176" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AN176" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO176" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP176" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ176" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR176" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS176" s="1" t="n"/>
+      <c r="AT176" s="1" t="n"/>
+      <c r="AU176" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV176" s="1" t="n"/>
+      <c r="AW176" s="1" t="n"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -25026,6 +28692,26 @@
       <c r="AM177" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN177" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO177" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP177" s="1" t="n"/>
+      <c r="AQ177" s="1" t="n"/>
+      <c r="AR177" s="1" t="n"/>
+      <c r="AS177" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT177" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU177" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV177" s="1" t="n"/>
+      <c r="AW177" s="1" t="n"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -25169,6 +28855,36 @@
       <c r="AM178" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN178" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO178" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP178" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ178" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR178" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS178" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT178" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU178" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV178" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW178" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -25312,6 +29028,123 @@
       <c r="AM179" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="AN179" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO179" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP179" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ179" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR179" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS179" s="1" t="n"/>
+      <c r="AT179" s="1" t="n"/>
+      <c r="AU179" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV179" s="1" t="n"/>
+      <c r="AW179" s="1" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2994641000033116</t>
+        </is>
+      </c>
+      <c r="B180" s="1" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>4995011000001107</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Niaspan titration pack (Abbott Laboratories Ltd)</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Niaspan titration pack</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>02120000</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>0212000U0BFADAY</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>02120000</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>Niaspan titration pack</t>
+        </is>
+      </c>
+      <c r="N180" s="1" t="n"/>
+      <c r="O180" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P180" s="1" t="n"/>
+      <c r="Q180" s="1" t="n"/>
+      <c r="R180" s="1" t="n"/>
+      <c r="S180" s="1" t="n"/>
+      <c r="T180" s="1" t="n"/>
+      <c r="U180" s="1" t="n"/>
+      <c r="V180" s="1" t="n"/>
+      <c r="W180" s="1" t="n"/>
+      <c r="X180" s="1" t="n"/>
+      <c r="Y180" s="1" t="n"/>
+      <c r="Z180" s="1" t="n"/>
+      <c r="AA180" s="1" t="n"/>
+      <c r="AB180" s="1" t="n"/>
+      <c r="AC180" s="1" t="n"/>
+      <c r="AD180" s="1" t="n"/>
+      <c r="AE180" s="1" t="n"/>
+      <c r="AF180" s="1" t="n"/>
+      <c r="AG180" s="1" t="n"/>
+      <c r="AH180" s="1" t="n"/>
+      <c r="AI180" s="1" t="n"/>
+      <c r="AJ180" s="1" t="n"/>
+      <c r="AK180" s="1" t="n"/>
+      <c r="AL180" s="1" t="n"/>
+      <c r="AM180" s="1" t="n"/>
+      <c r="AN180" s="1" t="n"/>
+      <c r="AO180" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP180" s="1" t="n"/>
+      <c r="AQ180" s="1" t="n"/>
+      <c r="AR180" s="1" t="n"/>
+      <c r="AS180" s="1" t="n"/>
+      <c r="AT180" s="1" t="n"/>
+      <c r="AU180" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV180" s="1" t="n"/>
+      <c r="AW180" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/codelists/statins_raw.xlsx
+++ b/codelists/statins_raw.xlsx
@@ -410,7 +410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW180"/>
+  <dimension ref="A1:AX180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.48" customWidth="1" min="1" max="1"/>
@@ -427,7 +427,7 @@
     <col width="12.88" customWidth="1" min="12" max="12"/>
     <col width="57.04" customWidth="1" min="13" max="13"/>
     <col width="8.280000000000001" customWidth="1" min="14" max="14"/>
-    <col width="7.36" customWidth="1" min="15" max="15"/>
+    <col width="14.72" customWidth="1" min="15" max="15"/>
     <col width="9.200000000000001" customWidth="1" min="16" max="16"/>
     <col width="11.04" customWidth="1" min="17" max="17"/>
     <col width="12.88" customWidth="1" min="18" max="18"/>
@@ -452,16 +452,17 @@
     <col width="11.96" customWidth="1" min="37" max="37"/>
     <col width="12.88" customWidth="1" min="38" max="38"/>
     <col width="11.96" customWidth="1" min="39" max="39"/>
-    <col width="12.88" customWidth="1" min="40" max="40"/>
-    <col width="17.48" customWidth="1" min="41" max="41"/>
-    <col width="11.04" customWidth="1" min="42" max="42"/>
+    <col width="7.36" customWidth="1" min="40" max="40"/>
+    <col width="20.24" customWidth="1" min="41" max="41"/>
+    <col width="17.48" customWidth="1" min="42" max="42"/>
     <col width="11.04" customWidth="1" min="43" max="43"/>
     <col width="11.04" customWidth="1" min="44" max="44"/>
-    <col width="10.12" customWidth="1" min="45" max="45"/>
-    <col width="11.04" customWidth="1" min="46" max="46"/>
+    <col width="11.04" customWidth="1" min="45" max="45"/>
+    <col width="10.12" customWidth="1" min="46" max="46"/>
     <col width="11.04" customWidth="1" min="47" max="47"/>
-    <col width="23" customWidth="1" min="48" max="48"/>
-    <col width="25.76" customWidth="1" min="49" max="49"/>
+    <col width="11.04" customWidth="1" min="48" max="48"/>
+    <col width="23" customWidth="1" min="49" max="49"/>
+    <col width="25.76" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -537,175 +538,180 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>lipid_lowering</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>acipimox</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>alirocumab</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>atorvastatin</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>bempedoic</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>bezafibrate</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>cerivastatin</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>ciprofibrate</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>colesevelam</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>colestipol</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>colestyramine</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>evolocumab</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ezetimibe</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>fenofibrate</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>fluvastatin</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>gemfibrozil</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>icosapent</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>inclisiran</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>lomitapide</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>nicotinic</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>omega</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>policosanol</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>pravastatin</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>rosuvastatin</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>simvastatin</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
           <t>statin</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>acipimox</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>alirocumab</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>atorvastatin</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>bempedoic</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>bezafibrate</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>cerivastatin</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>ciprofibrate</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>colesevelam</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>colestipol</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>colestyramine</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>evolocumab</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>ezetimibe</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>fenofibrate</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>fluvastatin</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>gemfibrozil</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>icosapent</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>inclisiran</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>lomitapide</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>nicotinic</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>omega</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>policosanol</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>pravastatin</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>rosuvastatin</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>simvastatin</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>statin_count</t>
-        </is>
-      </c>
       <c r="AO1" t="inlineStr">
         <is>
+          <t>lipid_lowering_count</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
           <t>external_codelist</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>lshtm_2102</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>lshtm_2199</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>lshtm_2470</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>hdruk_972</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>hdruk_1013</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>hdruk_1600</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>oc_openpresc_allstatins</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>oc_openpresc_lowmedstatins</t>
         </is>
@@ -856,11 +862,14 @@
       <c r="AR2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AS2" s="1" t="n"/>
+      <c r="AS2" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AT2" s="1" t="n"/>
       <c r="AU2" s="1" t="n"/>
       <c r="AV2" s="1" t="n"/>
       <c r="AW2" s="1" t="n"/>
+      <c r="AX2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1007,11 +1016,14 @@
       <c r="AR3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AS3" s="1" t="n"/>
+      <c r="AS3" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AT3" s="1" t="n"/>
       <c r="AU3" s="1" t="n"/>
       <c r="AV3" s="1" t="n"/>
       <c r="AW3" s="1" t="n"/>
+      <c r="AX3" s="1" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1182,7 +1194,10 @@
       <c r="AV4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AW4" s="1" t="n"/>
+      <c r="AW4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX4" s="1" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1353,7 +1368,10 @@
       <c r="AV5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AW5" s="1" t="n"/>
+      <c r="AW5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX5" s="1" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1525,6 +1543,9 @@
         <v>1</v>
       </c>
       <c r="AW6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX6" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1673,11 +1694,14 @@
       <c r="AR7" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AS7" s="1" t="n"/>
+      <c r="AS7" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AT7" s="1" t="n"/>
       <c r="AU7" s="1" t="n"/>
       <c r="AV7" s="1" t="n"/>
       <c r="AW7" s="1" t="n"/>
+      <c r="AX7" s="1" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1848,7 +1872,10 @@
       <c r="AV8" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AW8" s="1" t="n"/>
+      <c r="AW8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX8" s="1" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1981,9 +2008,11 @@
         <v>0</v>
       </c>
       <c r="AN9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO9" s="1" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="AO9" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP9" s="1" t="n"/>
       <c r="AQ9" s="1" t="n"/>
       <c r="AR9" s="1" t="n"/>
@@ -1992,6 +2021,7 @@
       <c r="AU9" s="1" t="n"/>
       <c r="AV9" s="1" t="n"/>
       <c r="AW9" s="1" t="n"/>
+      <c r="AX9" s="1" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2138,11 +2168,14 @@
       <c r="AR10" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AS10" s="1" t="n"/>
+      <c r="AS10" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AT10" s="1" t="n"/>
       <c r="AU10" s="1" t="n"/>
       <c r="AV10" s="1" t="n"/>
       <c r="AW10" s="1" t="n"/>
+      <c r="AX10" s="1" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2289,11 +2322,14 @@
       <c r="AR11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AS11" s="1" t="n"/>
+      <c r="AS11" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AT11" s="1" t="n"/>
       <c r="AU11" s="1" t="n"/>
       <c r="AV11" s="1" t="n"/>
       <c r="AW11" s="1" t="n"/>
+      <c r="AX11" s="1" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2440,11 +2476,14 @@
       <c r="AR12" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AS12" s="1" t="n"/>
+      <c r="AS12" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AT12" s="1" t="n"/>
       <c r="AU12" s="1" t="n"/>
       <c r="AV12" s="1" t="n"/>
       <c r="AW12" s="1" t="n"/>
+      <c r="AX12" s="1" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2591,11 +2630,14 @@
       <c r="AR13" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AS13" s="1" t="n"/>
+      <c r="AS13" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AT13" s="1" t="n"/>
       <c r="AU13" s="1" t="n"/>
       <c r="AV13" s="1" t="n"/>
       <c r="AW13" s="1" t="n"/>
+      <c r="AX13" s="1" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2740,25 +2782,28 @@
         <v>0</v>
       </c>
       <c r="AN14" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO14" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP14" s="1" t="n"/>
+      <c r="AP14" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ14" s="1" t="n"/>
       <c r="AR14" s="1" t="n"/>
-      <c r="AS14" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS14" s="1" t="n"/>
       <c r="AT14" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU14" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV14" s="1" t="n"/>
+      <c r="AV14" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW14" s="1" t="n"/>
+      <c r="AX14" s="1" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2905,11 +2950,14 @@
       <c r="AR15" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AS15" s="1" t="n"/>
+      <c r="AS15" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AT15" s="1" t="n"/>
       <c r="AU15" s="1" t="n"/>
       <c r="AV15" s="1" t="n"/>
       <c r="AW15" s="1" t="n"/>
+      <c r="AX15" s="1" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3056,11 +3104,14 @@
       <c r="AR16" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AS16" s="1" t="n"/>
+      <c r="AS16" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AT16" s="1" t="n"/>
       <c r="AU16" s="1" t="n"/>
       <c r="AV16" s="1" t="n"/>
       <c r="AW16" s="1" t="n"/>
+      <c r="AX16" s="1" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3207,11 +3258,14 @@
       <c r="AR17" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AS17" s="1" t="n"/>
+      <c r="AS17" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AT17" s="1" t="n"/>
       <c r="AU17" s="1" t="n"/>
       <c r="AV17" s="1" t="n"/>
       <c r="AW17" s="1" t="n"/>
+      <c r="AX17" s="1" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3344,9 +3398,11 @@
         <v>0</v>
       </c>
       <c r="AN18" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO18" s="1" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="AO18" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP18" s="1" t="n"/>
       <c r="AQ18" s="1" t="n"/>
       <c r="AR18" s="1" t="n"/>
@@ -3355,6 +3411,7 @@
       <c r="AU18" s="1" t="n"/>
       <c r="AV18" s="1" t="n"/>
       <c r="AW18" s="1" t="n"/>
+      <c r="AX18" s="1" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3499,25 +3556,28 @@
         <v>0</v>
       </c>
       <c r="AN19" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO19" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP19" s="1" t="n"/>
+      <c r="AP19" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ19" s="1" t="n"/>
       <c r="AR19" s="1" t="n"/>
-      <c r="AS19" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS19" s="1" t="n"/>
       <c r="AT19" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU19" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV19" s="1" t="n"/>
+      <c r="AV19" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW19" s="1" t="n"/>
+      <c r="AX19" s="1" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3691,6 +3751,9 @@
       <c r="AW20" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AX20" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3864,6 +3927,9 @@
       <c r="AW21" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AX21" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4035,6 +4101,9 @@
         <v>1</v>
       </c>
       <c r="AW22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX22" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4169,9 +4238,11 @@
         <v>0</v>
       </c>
       <c r="AN23" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO23" s="1" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="AO23" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP23" s="1" t="n"/>
       <c r="AQ23" s="1" t="n"/>
       <c r="AR23" s="1" t="n"/>
@@ -4180,6 +4251,7 @@
       <c r="AU23" s="1" t="n"/>
       <c r="AV23" s="1" t="n"/>
       <c r="AW23" s="1" t="n"/>
+      <c r="AX23" s="1" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4324,25 +4396,28 @@
         <v>0</v>
       </c>
       <c r="AN24" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO24" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP24" s="1" t="n"/>
+      <c r="AP24" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ24" s="1" t="n"/>
       <c r="AR24" s="1" t="n"/>
-      <c r="AS24" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS24" s="1" t="n"/>
       <c r="AT24" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU24" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV24" s="1" t="n"/>
+      <c r="AV24" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW24" s="1" t="n"/>
+      <c r="AX24" s="1" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4514,6 +4589,9 @@
         <v>1</v>
       </c>
       <c r="AW25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX25" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4648,9 +4726,11 @@
         <v>0</v>
       </c>
       <c r="AN26" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO26" s="1" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="AO26" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP26" s="1" t="n"/>
       <c r="AQ26" s="1" t="n"/>
       <c r="AR26" s="1" t="n"/>
@@ -4659,6 +4739,7 @@
       <c r="AU26" s="1" t="n"/>
       <c r="AV26" s="1" t="n"/>
       <c r="AW26" s="1" t="n"/>
+      <c r="AX26" s="1" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4791,9 +4872,11 @@
         <v>0</v>
       </c>
       <c r="AN27" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO27" s="1" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="AO27" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP27" s="1" t="n"/>
       <c r="AQ27" s="1" t="n"/>
       <c r="AR27" s="1" t="n"/>
@@ -4802,6 +4885,7 @@
       <c r="AU27" s="1" t="n"/>
       <c r="AV27" s="1" t="n"/>
       <c r="AW27" s="1" t="n"/>
+      <c r="AX27" s="1" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4946,25 +5030,28 @@
         <v>0</v>
       </c>
       <c r="AN28" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO28" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP28" s="1" t="n"/>
+      <c r="AP28" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ28" s="1" t="n"/>
       <c r="AR28" s="1" t="n"/>
-      <c r="AS28" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS28" s="1" t="n"/>
       <c r="AT28" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU28" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV28" s="1" t="n"/>
+      <c r="AV28" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW28" s="1" t="n"/>
+      <c r="AX28" s="1" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5097,9 +5184,11 @@
         <v>0</v>
       </c>
       <c r="AN29" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO29" s="1" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="AO29" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP29" s="1" t="n"/>
       <c r="AQ29" s="1" t="n"/>
       <c r="AR29" s="1" t="n"/>
@@ -5108,6 +5197,7 @@
       <c r="AU29" s="1" t="n"/>
       <c r="AV29" s="1" t="n"/>
       <c r="AW29" s="1" t="n"/>
+      <c r="AX29" s="1" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5254,11 +5344,14 @@
       <c r="AR30" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AS30" s="1" t="n"/>
+      <c r="AS30" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AT30" s="1" t="n"/>
       <c r="AU30" s="1" t="n"/>
       <c r="AV30" s="1" t="n"/>
       <c r="AW30" s="1" t="n"/>
+      <c r="AX30" s="1" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5391,9 +5484,11 @@
         <v>0</v>
       </c>
       <c r="AN31" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO31" s="1" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="AO31" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP31" s="1" t="n"/>
       <c r="AQ31" s="1" t="n"/>
       <c r="AR31" s="1" t="n"/>
@@ -5402,6 +5497,7 @@
       <c r="AU31" s="1" t="n"/>
       <c r="AV31" s="1" t="n"/>
       <c r="AW31" s="1" t="n"/>
+      <c r="AX31" s="1" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5546,25 +5642,28 @@
         <v>0</v>
       </c>
       <c r="AN32" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO32" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP32" s="1" t="n"/>
+      <c r="AP32" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ32" s="1" t="n"/>
       <c r="AR32" s="1" t="n"/>
-      <c r="AS32" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS32" s="1" t="n"/>
       <c r="AT32" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU32" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV32" s="1" t="n"/>
+      <c r="AV32" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW32" s="1" t="n"/>
+      <c r="AX32" s="1" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5736,6 +5835,9 @@
         <v>1</v>
       </c>
       <c r="AW33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX33" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5884,11 +5986,14 @@
       <c r="AR34" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AS34" s="1" t="n"/>
+      <c r="AS34" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AT34" s="1" t="n"/>
       <c r="AU34" s="1" t="n"/>
       <c r="AV34" s="1" t="n"/>
       <c r="AW34" s="1" t="n"/>
+      <c r="AX34" s="1" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6060,6 +6165,9 @@
         <v>1</v>
       </c>
       <c r="AW35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX35" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6194,9 +6302,11 @@
         <v>0</v>
       </c>
       <c r="AN36" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO36" s="1" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="AO36" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP36" s="1" t="n"/>
       <c r="AQ36" s="1" t="n"/>
       <c r="AR36" s="1" t="n"/>
@@ -6205,6 +6315,7 @@
       <c r="AU36" s="1" t="n"/>
       <c r="AV36" s="1" t="n"/>
       <c r="AW36" s="1" t="n"/>
+      <c r="AX36" s="1" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6378,6 +6489,9 @@
       <c r="AW37" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AX37" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6548,7 +6662,10 @@
       <c r="AV38" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AW38" s="1" t="n"/>
+      <c r="AW38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX38" s="1" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6681,9 +6798,11 @@
         <v>0</v>
       </c>
       <c r="AN39" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO39" s="1" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="AO39" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP39" s="1" t="n"/>
       <c r="AQ39" s="1" t="n"/>
       <c r="AR39" s="1" t="n"/>
@@ -6692,6 +6811,7 @@
       <c r="AU39" s="1" t="n"/>
       <c r="AV39" s="1" t="n"/>
       <c r="AW39" s="1" t="n"/>
+      <c r="AX39" s="1" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6836,25 +6956,28 @@
         <v>0</v>
       </c>
       <c r="AN40" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO40" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP40" s="1" t="n"/>
+      <c r="AP40" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ40" s="1" t="n"/>
       <c r="AR40" s="1" t="n"/>
-      <c r="AS40" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS40" s="1" t="n"/>
       <c r="AT40" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU40" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV40" s="1" t="n"/>
+      <c r="AV40" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW40" s="1" t="n"/>
+      <c r="AX40" s="1" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6999,25 +7122,28 @@
         <v>0</v>
       </c>
       <c r="AN41" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO41" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP41" s="1" t="n"/>
+      <c r="AP41" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ41" s="1" t="n"/>
       <c r="AR41" s="1" t="n"/>
-      <c r="AS41" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS41" s="1" t="n"/>
       <c r="AT41" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU41" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV41" s="1" t="n"/>
+      <c r="AV41" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW41" s="1" t="n"/>
+      <c r="AX41" s="1" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -7162,25 +7288,28 @@
         <v>0</v>
       </c>
       <c r="AN42" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO42" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP42" s="1" t="n"/>
+      <c r="AP42" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ42" s="1" t="n"/>
       <c r="AR42" s="1" t="n"/>
-      <c r="AS42" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS42" s="1" t="n"/>
       <c r="AT42" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU42" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV42" s="1" t="n"/>
+      <c r="AV42" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW42" s="1" t="n"/>
+      <c r="AX42" s="1" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -7313,11 +7442,11 @@
         <v>1</v>
       </c>
       <c r="AN43" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO43" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AO43" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="AP43" s="1" t="n">
         <v>1</v>
       </c>
@@ -7327,11 +7456,14 @@
       <c r="AR43" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AS43" s="1" t="n"/>
+      <c r="AS43" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AT43" s="1" t="n"/>
       <c r="AU43" s="1" t="n"/>
       <c r="AV43" s="1" t="n"/>
       <c r="AW43" s="1" t="n"/>
+      <c r="AX43" s="1" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -7476,25 +7608,28 @@
         <v>0</v>
       </c>
       <c r="AN44" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO44" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP44" s="1" t="n"/>
+      <c r="AP44" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ44" s="1" t="n"/>
       <c r="AR44" s="1" t="n"/>
-      <c r="AS44" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS44" s="1" t="n"/>
       <c r="AT44" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU44" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV44" s="1" t="n"/>
+      <c r="AV44" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW44" s="1" t="n"/>
+      <c r="AX44" s="1" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -7668,6 +7803,9 @@
       <c r="AW45" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AX45" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -7812,25 +7950,28 @@
         <v>0</v>
       </c>
       <c r="AN46" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO46" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP46" s="1" t="n"/>
+      <c r="AP46" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ46" s="1" t="n"/>
       <c r="AR46" s="1" t="n"/>
-      <c r="AS46" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS46" s="1" t="n"/>
       <c r="AT46" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU46" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV46" s="1" t="n"/>
+      <c r="AV46" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW46" s="1" t="n"/>
+      <c r="AX46" s="1" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -7975,25 +8116,28 @@
         <v>0</v>
       </c>
       <c r="AN47" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO47" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP47" s="1" t="n"/>
+      <c r="AP47" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ47" s="1" t="n"/>
       <c r="AR47" s="1" t="n"/>
-      <c r="AS47" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS47" s="1" t="n"/>
       <c r="AT47" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU47" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV47" s="1" t="n"/>
+      <c r="AV47" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW47" s="1" t="n"/>
+      <c r="AX47" s="1" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -8138,25 +8282,28 @@
         <v>0</v>
       </c>
       <c r="AN48" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO48" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP48" s="1" t="n"/>
+      <c r="AP48" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ48" s="1" t="n"/>
       <c r="AR48" s="1" t="n"/>
-      <c r="AS48" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS48" s="1" t="n"/>
       <c r="AT48" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU48" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV48" s="1" t="n"/>
+      <c r="AV48" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW48" s="1" t="n"/>
+      <c r="AX48" s="1" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -8289,9 +8436,11 @@
         <v>0</v>
       </c>
       <c r="AN49" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO49" s="1" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="AO49" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP49" s="1" t="n"/>
       <c r="AQ49" s="1" t="n"/>
       <c r="AR49" s="1" t="n"/>
@@ -8300,6 +8449,7 @@
       <c r="AU49" s="1" t="n"/>
       <c r="AV49" s="1" t="n"/>
       <c r="AW49" s="1" t="n"/>
+      <c r="AX49" s="1" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -8446,11 +8596,14 @@
       <c r="AR50" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AS50" s="1" t="n"/>
+      <c r="AS50" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AT50" s="1" t="n"/>
       <c r="AU50" s="1" t="n"/>
       <c r="AV50" s="1" t="n"/>
       <c r="AW50" s="1" t="n"/>
+      <c r="AX50" s="1" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -8621,7 +8774,10 @@
       <c r="AV51" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AW51" s="1" t="n"/>
+      <c r="AW51" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX51" s="1" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -8792,7 +8948,10 @@
       <c r="AV52" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AW52" s="1" t="n"/>
+      <c r="AW52" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX52" s="1" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -8966,6 +9125,9 @@
       <c r="AW53" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AX53" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -9124,15 +9286,18 @@
       <c r="AR54" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AS54" s="1" t="n"/>
+      <c r="AS54" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AT54" s="1" t="n"/>
-      <c r="AU54" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AU54" s="1" t="n"/>
       <c r="AV54" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AW54" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX54" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9267,11 +9432,11 @@
         <v>1</v>
       </c>
       <c r="AN55" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO55" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AO55" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="AP55" s="1" t="n">
         <v>1</v>
       </c>
@@ -9281,11 +9446,14 @@
       <c r="AR55" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AS55" s="1" t="n"/>
+      <c r="AS55" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AT55" s="1" t="n"/>
       <c r="AU55" s="1" t="n"/>
       <c r="AV55" s="1" t="n"/>
       <c r="AW55" s="1" t="n"/>
+      <c r="AX55" s="1" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -9459,6 +9627,9 @@
       <c r="AW56" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AX56" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -9603,25 +9774,28 @@
         <v>0</v>
       </c>
       <c r="AN57" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO57" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP57" s="1" t="n"/>
+      <c r="AP57" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ57" s="1" t="n"/>
       <c r="AR57" s="1" t="n"/>
-      <c r="AS57" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS57" s="1" t="n"/>
       <c r="AT57" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU57" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV57" s="1" t="n"/>
+      <c r="AV57" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW57" s="1" t="n"/>
+      <c r="AX57" s="1" t="n"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -9754,9 +9928,11 @@
         <v>0</v>
       </c>
       <c r="AN58" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO58" s="1" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="AO58" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP58" s="1" t="n"/>
       <c r="AQ58" s="1" t="n"/>
       <c r="AR58" s="1" t="n"/>
@@ -9765,6 +9941,7 @@
       <c r="AU58" s="1" t="n"/>
       <c r="AV58" s="1" t="n"/>
       <c r="AW58" s="1" t="n"/>
+      <c r="AX58" s="1" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -9911,11 +10088,14 @@
       <c r="AR59" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AS59" s="1" t="n"/>
+      <c r="AS59" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AT59" s="1" t="n"/>
       <c r="AU59" s="1" t="n"/>
       <c r="AV59" s="1" t="n"/>
       <c r="AW59" s="1" t="n"/>
+      <c r="AX59" s="1" t="n"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -10044,9 +10224,11 @@
         <v>0</v>
       </c>
       <c r="AN60" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO60" s="1" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="AO60" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP60" s="1" t="n"/>
       <c r="AQ60" s="1" t="n"/>
       <c r="AR60" s="1" t="n"/>
@@ -10055,6 +10237,7 @@
       <c r="AU60" s="1" t="n"/>
       <c r="AV60" s="1" t="n"/>
       <c r="AW60" s="1" t="n"/>
+      <c r="AX60" s="1" t="n"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -10199,25 +10382,28 @@
         <v>0</v>
       </c>
       <c r="AN61" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO61" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP61" s="1" t="n"/>
+      <c r="AP61" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ61" s="1" t="n"/>
       <c r="AR61" s="1" t="n"/>
-      <c r="AS61" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS61" s="1" t="n"/>
       <c r="AT61" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU61" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV61" s="1" t="n"/>
+      <c r="AV61" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW61" s="1" t="n"/>
+      <c r="AX61" s="1" t="n"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -10391,6 +10577,9 @@
       <c r="AW62" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AX62" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -10561,7 +10750,10 @@
       <c r="AV63" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AW63" s="1" t="n"/>
+      <c r="AW63" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX63" s="1" t="n"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -10694,9 +10886,11 @@
         <v>0</v>
       </c>
       <c r="AN64" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO64" s="1" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="AO64" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP64" s="1" t="n"/>
       <c r="AQ64" s="1" t="n"/>
       <c r="AR64" s="1" t="n"/>
@@ -10705,6 +10899,7 @@
       <c r="AU64" s="1" t="n"/>
       <c r="AV64" s="1" t="n"/>
       <c r="AW64" s="1" t="n"/>
+      <c r="AX64" s="1" t="n"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -10851,11 +11046,14 @@
       <c r="AR65" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AS65" s="1" t="n"/>
+      <c r="AS65" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AT65" s="1" t="n"/>
       <c r="AU65" s="1" t="n"/>
       <c r="AV65" s="1" t="n"/>
       <c r="AW65" s="1" t="n"/>
+      <c r="AX65" s="1" t="n"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -11000,25 +11198,28 @@
         <v>0</v>
       </c>
       <c r="AN66" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO66" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP66" s="1" t="n"/>
+      <c r="AP66" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ66" s="1" t="n"/>
       <c r="AR66" s="1" t="n"/>
-      <c r="AS66" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS66" s="1" t="n"/>
       <c r="AT66" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU66" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV66" s="1" t="n"/>
+      <c r="AV66" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW66" s="1" t="n"/>
+      <c r="AX66" s="1" t="n"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -11151,11 +11352,11 @@
         <v>1</v>
       </c>
       <c r="AN67" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO67" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AO67" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="AP67" s="1" t="n">
         <v>1</v>
       </c>
@@ -11165,11 +11366,14 @@
       <c r="AR67" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AS67" s="1" t="n"/>
+      <c r="AS67" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AT67" s="1" t="n"/>
       <c r="AU67" s="1" t="n"/>
       <c r="AV67" s="1" t="n"/>
       <c r="AW67" s="1" t="n"/>
+      <c r="AX67" s="1" t="n"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -11343,6 +11547,9 @@
       <c r="AW68" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AX68" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -11516,6 +11723,9 @@
       <c r="AW69" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AX69" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -11689,6 +11899,9 @@
       <c r="AW70" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AX70" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -11833,25 +12046,28 @@
         <v>0</v>
       </c>
       <c r="AN71" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO71" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP71" s="1" t="n"/>
+      <c r="AP71" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ71" s="1" t="n"/>
       <c r="AR71" s="1" t="n"/>
-      <c r="AS71" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS71" s="1" t="n"/>
       <c r="AT71" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU71" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV71" s="1" t="n"/>
+      <c r="AV71" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW71" s="1" t="n"/>
+      <c r="AX71" s="1" t="n"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -12022,7 +12238,10 @@
       <c r="AV72" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AW72" s="1" t="n"/>
+      <c r="AW72" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX72" s="1" t="n"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -12181,13 +12400,16 @@
       <c r="AR73" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AS73" s="1" t="n"/>
+      <c r="AS73" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AT73" s="1" t="n"/>
-      <c r="AU73" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV73" s="1" t="n"/>
+      <c r="AU73" s="1" t="n"/>
+      <c r="AV73" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW73" s="1" t="n"/>
+      <c r="AX73" s="1" t="n"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -12358,7 +12580,10 @@
       <c r="AV74" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AW74" s="1" t="n"/>
+      <c r="AW74" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX74" s="1" t="n"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -12530,6 +12755,9 @@
         <v>1</v>
       </c>
       <c r="AW75" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX75" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12636,9 +12864,11 @@
         <v>0</v>
       </c>
       <c r="AN76" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO76" s="1" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="AO76" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP76" s="1" t="n"/>
       <c r="AQ76" s="1" t="n"/>
       <c r="AR76" s="1" t="n"/>
@@ -12647,6 +12877,7 @@
       <c r="AU76" s="1" t="n"/>
       <c r="AV76" s="1" t="n"/>
       <c r="AW76" s="1" t="n"/>
+      <c r="AX76" s="1" t="n"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -12814,8 +13045,11 @@
       <c r="AU77" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV77" s="1" t="n"/>
+      <c r="AV77" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW77" s="1" t="n"/>
+      <c r="AX77" s="1" t="n"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -12983,8 +13217,11 @@
       <c r="AU78" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV78" s="1" t="n"/>
+      <c r="AV78" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW78" s="1" t="n"/>
+      <c r="AX78" s="1" t="n"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -13158,6 +13395,9 @@
       <c r="AW79" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AX79" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -13328,7 +13568,10 @@
       <c r="AV80" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AW80" s="1" t="n"/>
+      <c r="AW80" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX80" s="1" t="n"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -13473,25 +13716,28 @@
         <v>0</v>
       </c>
       <c r="AN81" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO81" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP81" s="1" t="n"/>
+      <c r="AP81" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ81" s="1" t="n"/>
       <c r="AR81" s="1" t="n"/>
-      <c r="AS81" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS81" s="1" t="n"/>
       <c r="AT81" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU81" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV81" s="1" t="n"/>
+      <c r="AV81" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW81" s="1" t="n"/>
+      <c r="AX81" s="1" t="n"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -13600,9 +13846,11 @@
         <v>0</v>
       </c>
       <c r="AN82" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO82" s="1" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="AO82" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP82" s="1" t="n"/>
       <c r="AQ82" s="1" t="n"/>
       <c r="AR82" s="1" t="n"/>
@@ -13611,6 +13859,7 @@
       <c r="AU82" s="1" t="n"/>
       <c r="AV82" s="1" t="n"/>
       <c r="AW82" s="1" t="n"/>
+      <c r="AX82" s="1" t="n"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -13755,25 +14004,28 @@
         <v>0</v>
       </c>
       <c r="AN83" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO83" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP83" s="1" t="n"/>
+      <c r="AP83" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ83" s="1" t="n"/>
       <c r="AR83" s="1" t="n"/>
-      <c r="AS83" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS83" s="1" t="n"/>
       <c r="AT83" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU83" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV83" s="1" t="n"/>
+      <c r="AV83" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW83" s="1" t="n"/>
+      <c r="AX83" s="1" t="n"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -13918,25 +14170,28 @@
         <v>0</v>
       </c>
       <c r="AN84" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO84" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP84" s="1" t="n"/>
+      <c r="AP84" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ84" s="1" t="n"/>
       <c r="AR84" s="1" t="n"/>
-      <c r="AS84" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS84" s="1" t="n"/>
       <c r="AT84" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU84" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV84" s="1" t="n"/>
+      <c r="AV84" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW84" s="1" t="n"/>
+      <c r="AX84" s="1" t="n"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -14081,25 +14336,28 @@
         <v>0</v>
       </c>
       <c r="AN85" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO85" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP85" s="1" t="n"/>
+      <c r="AP85" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ85" s="1" t="n"/>
       <c r="AR85" s="1" t="n"/>
-      <c r="AS85" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS85" s="1" t="n"/>
       <c r="AT85" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU85" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV85" s="1" t="n"/>
+      <c r="AV85" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW85" s="1" t="n"/>
+      <c r="AX85" s="1" t="n"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -14273,6 +14531,9 @@
       <c r="AW86" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AX86" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -14431,13 +14692,16 @@
       <c r="AR87" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AS87" s="1" t="n"/>
+      <c r="AS87" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AT87" s="1" t="n"/>
-      <c r="AU87" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV87" s="1" t="n"/>
+      <c r="AU87" s="1" t="n"/>
+      <c r="AV87" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW87" s="1" t="n"/>
+      <c r="AX87" s="1" t="n"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -14542,9 +14806,11 @@
         <v>0</v>
       </c>
       <c r="AN88" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO88" s="1" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="AO88" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP88" s="1" t="n"/>
       <c r="AQ88" s="1" t="n"/>
       <c r="AR88" s="1" t="n"/>
@@ -14553,6 +14819,7 @@
       <c r="AU88" s="1" t="n"/>
       <c r="AV88" s="1" t="n"/>
       <c r="AW88" s="1" t="n"/>
+      <c r="AX88" s="1" t="n"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -14697,21 +14964,24 @@
         <v>0</v>
       </c>
       <c r="AN89" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO89" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP89" s="1" t="n"/>
+      <c r="AP89" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ89" s="1" t="n"/>
       <c r="AR89" s="1" t="n"/>
       <c r="AS89" s="1" t="n"/>
       <c r="AT89" s="1" t="n"/>
-      <c r="AU89" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV89" s="1" t="n"/>
+      <c r="AU89" s="1" t="n"/>
+      <c r="AV89" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW89" s="1" t="n"/>
+      <c r="AX89" s="1" t="n"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -14856,25 +15126,28 @@
         <v>0</v>
       </c>
       <c r="AN90" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO90" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP90" s="1" t="n"/>
+      <c r="AP90" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ90" s="1" t="n"/>
       <c r="AR90" s="1" t="n"/>
-      <c r="AS90" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS90" s="1" t="n"/>
       <c r="AT90" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU90" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV90" s="1" t="n"/>
+      <c r="AV90" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW90" s="1" t="n"/>
+      <c r="AX90" s="1" t="n"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -15019,21 +15292,24 @@
         <v>0</v>
       </c>
       <c r="AN91" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO91" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP91" s="1" t="n"/>
+      <c r="AP91" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ91" s="1" t="n"/>
       <c r="AR91" s="1" t="n"/>
       <c r="AS91" s="1" t="n"/>
       <c r="AT91" s="1" t="n"/>
-      <c r="AU91" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV91" s="1" t="n"/>
+      <c r="AU91" s="1" t="n"/>
+      <c r="AV91" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW91" s="1" t="n"/>
+      <c r="AX91" s="1" t="n"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -15178,25 +15454,28 @@
         <v>0</v>
       </c>
       <c r="AN92" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO92" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP92" s="1" t="n"/>
+      <c r="AP92" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ92" s="1" t="n"/>
       <c r="AR92" s="1" t="n"/>
-      <c r="AS92" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS92" s="1" t="n"/>
       <c r="AT92" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU92" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV92" s="1" t="n"/>
+      <c r="AV92" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW92" s="1" t="n"/>
+      <c r="AX92" s="1" t="n"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -15341,25 +15620,28 @@
         <v>0</v>
       </c>
       <c r="AN93" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO93" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP93" s="1" t="n"/>
+      <c r="AP93" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ93" s="1" t="n"/>
       <c r="AR93" s="1" t="n"/>
-      <c r="AS93" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS93" s="1" t="n"/>
       <c r="AT93" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU93" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV93" s="1" t="n"/>
+      <c r="AV93" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW93" s="1" t="n"/>
+      <c r="AX93" s="1" t="n"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -15504,21 +15786,24 @@
         <v>0</v>
       </c>
       <c r="AN94" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO94" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP94" s="1" t="n"/>
+      <c r="AP94" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ94" s="1" t="n"/>
       <c r="AR94" s="1" t="n"/>
       <c r="AS94" s="1" t="n"/>
       <c r="AT94" s="1" t="n"/>
-      <c r="AU94" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV94" s="1" t="n"/>
+      <c r="AU94" s="1" t="n"/>
+      <c r="AV94" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW94" s="1" t="n"/>
+      <c r="AX94" s="1" t="n"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -15663,21 +15948,24 @@
         <v>0</v>
       </c>
       <c r="AN95" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO95" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP95" s="1" t="n"/>
+      <c r="AP95" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ95" s="1" t="n"/>
       <c r="AR95" s="1" t="n"/>
       <c r="AS95" s="1" t="n"/>
       <c r="AT95" s="1" t="n"/>
-      <c r="AU95" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV95" s="1" t="n"/>
+      <c r="AU95" s="1" t="n"/>
+      <c r="AV95" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW95" s="1" t="n"/>
+      <c r="AX95" s="1" t="n"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -15822,11 +16110,11 @@
         <v>1</v>
       </c>
       <c r="AN96" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO96" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AO96" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="AP96" s="1" t="n">
         <v>1</v>
       </c>
@@ -15849,6 +16137,9 @@
         <v>1</v>
       </c>
       <c r="AW96" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX96" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -15995,11 +16286,11 @@
         <v>1</v>
       </c>
       <c r="AN97" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO97" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AO97" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="AP97" s="1" t="n">
         <v>1</v>
       </c>
@@ -16022,6 +16313,9 @@
         <v>1</v>
       </c>
       <c r="AW97" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX97" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16132,9 +16426,11 @@
         <v>0</v>
       </c>
       <c r="AN98" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO98" s="1" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="AO98" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP98" s="1" t="n"/>
       <c r="AQ98" s="1" t="n"/>
       <c r="AR98" s="1" t="n"/>
@@ -16143,6 +16439,7 @@
       <c r="AU98" s="1" t="n"/>
       <c r="AV98" s="1" t="n"/>
       <c r="AW98" s="1" t="n"/>
+      <c r="AX98" s="1" t="n"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -16287,23 +16584,26 @@
         <v>0</v>
       </c>
       <c r="AN99" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO99" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP99" s="1" t="n"/>
+      <c r="AP99" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ99" s="1" t="n"/>
       <c r="AR99" s="1" t="n"/>
-      <c r="AS99" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS99" s="1" t="n"/>
       <c r="AT99" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AU99" s="1" t="n"/>
+      <c r="AU99" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AV99" s="1" t="n"/>
       <c r="AW99" s="1" t="n"/>
+      <c r="AX99" s="1" t="n"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -16462,13 +16762,16 @@
       <c r="AR100" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AS100" s="1" t="n"/>
+      <c r="AS100" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AT100" s="1" t="n"/>
-      <c r="AU100" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV100" s="1" t="n"/>
+      <c r="AU100" s="1" t="n"/>
+      <c r="AV100" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW100" s="1" t="n"/>
+      <c r="AX100" s="1" t="n"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -16573,9 +16876,11 @@
         <v>0</v>
       </c>
       <c r="AN101" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO101" s="1" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="AO101" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP101" s="1" t="n"/>
       <c r="AQ101" s="1" t="n"/>
       <c r="AR101" s="1" t="n"/>
@@ -16584,6 +16889,7 @@
       <c r="AU101" s="1" t="n"/>
       <c r="AV101" s="1" t="n"/>
       <c r="AW101" s="1" t="n"/>
+      <c r="AX101" s="1" t="n"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -16742,13 +17048,16 @@
       <c r="AR102" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AS102" s="1" t="n"/>
+      <c r="AS102" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AT102" s="1" t="n"/>
-      <c r="AU102" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV102" s="1" t="n"/>
+      <c r="AU102" s="1" t="n"/>
+      <c r="AV102" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW102" s="1" t="n"/>
+      <c r="AX102" s="1" t="n"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -16922,6 +17231,9 @@
       <c r="AW103" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AX103" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -17066,25 +17378,28 @@
         <v>0</v>
       </c>
       <c r="AN104" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO104" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP104" s="1" t="n"/>
+      <c r="AP104" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ104" s="1" t="n"/>
       <c r="AR104" s="1" t="n"/>
-      <c r="AS104" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS104" s="1" t="n"/>
       <c r="AT104" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU104" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV104" s="1" t="n"/>
+      <c r="AV104" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW104" s="1" t="n"/>
+      <c r="AX104" s="1" t="n"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -17229,21 +17544,24 @@
         <v>0</v>
       </c>
       <c r="AN105" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO105" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP105" s="1" t="n"/>
+      <c r="AP105" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ105" s="1" t="n"/>
       <c r="AR105" s="1" t="n"/>
       <c r="AS105" s="1" t="n"/>
       <c r="AT105" s="1" t="n"/>
-      <c r="AU105" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV105" s="1" t="n"/>
+      <c r="AU105" s="1" t="n"/>
+      <c r="AV105" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW105" s="1" t="n"/>
+      <c r="AX105" s="1" t="n"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -17388,21 +17706,24 @@
         <v>0</v>
       </c>
       <c r="AN106" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO106" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP106" s="1" t="n"/>
+      <c r="AP106" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ106" s="1" t="n"/>
       <c r="AR106" s="1" t="n"/>
       <c r="AS106" s="1" t="n"/>
       <c r="AT106" s="1" t="n"/>
-      <c r="AU106" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV106" s="1" t="n"/>
+      <c r="AU106" s="1" t="n"/>
+      <c r="AV106" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW106" s="1" t="n"/>
+      <c r="AX106" s="1" t="n"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -17547,21 +17868,24 @@
         <v>0</v>
       </c>
       <c r="AN107" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO107" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP107" s="1" t="n"/>
+      <c r="AP107" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ107" s="1" t="n"/>
       <c r="AR107" s="1" t="n"/>
       <c r="AS107" s="1" t="n"/>
       <c r="AT107" s="1" t="n"/>
-      <c r="AU107" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV107" s="1" t="n"/>
+      <c r="AU107" s="1" t="n"/>
+      <c r="AV107" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW107" s="1" t="n"/>
+      <c r="AX107" s="1" t="n"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -17706,25 +18030,28 @@
         <v>0</v>
       </c>
       <c r="AN108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO108" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AO108" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP108" s="1" t="n"/>
+      <c r="AP108" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ108" s="1" t="n"/>
       <c r="AR108" s="1" t="n"/>
-      <c r="AS108" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS108" s="1" t="n"/>
       <c r="AT108" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU108" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV108" s="1" t="n"/>
+      <c r="AV108" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW108" s="1" t="n"/>
+      <c r="AX108" s="1" t="n"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -17869,21 +18196,24 @@
         <v>0</v>
       </c>
       <c r="AN109" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO109" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP109" s="1" t="n"/>
+      <c r="AP109" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ109" s="1" t="n"/>
       <c r="AR109" s="1" t="n"/>
       <c r="AS109" s="1" t="n"/>
       <c r="AT109" s="1" t="n"/>
-      <c r="AU109" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV109" s="1" t="n"/>
+      <c r="AU109" s="1" t="n"/>
+      <c r="AV109" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW109" s="1" t="n"/>
+      <c r="AX109" s="1" t="n"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -18051,8 +18381,11 @@
       <c r="AU110" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV110" s="1" t="n"/>
+      <c r="AV110" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW110" s="1" t="n"/>
+      <c r="AX110" s="1" t="n"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -18223,7 +18556,10 @@
       <c r="AV111" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AW111" s="1" t="n"/>
+      <c r="AW111" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX111" s="1" t="n"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -18368,25 +18704,28 @@
         <v>0</v>
       </c>
       <c r="AN112" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO112" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP112" s="1" t="n"/>
+      <c r="AP112" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ112" s="1" t="n"/>
       <c r="AR112" s="1" t="n"/>
-      <c r="AS112" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS112" s="1" t="n"/>
       <c r="AT112" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU112" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV112" s="1" t="n"/>
+      <c r="AV112" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW112" s="1" t="n"/>
+      <c r="AX112" s="1" t="n"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -18557,7 +18896,10 @@
       <c r="AV113" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AW113" s="1" t="n"/>
+      <c r="AW113" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX113" s="1" t="n"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -18728,7 +19070,10 @@
       <c r="AV114" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AW114" s="1" t="n"/>
+      <c r="AW114" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX114" s="1" t="n"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -18887,13 +19232,16 @@
       <c r="AR115" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AS115" s="1" t="n"/>
+      <c r="AS115" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AT115" s="1" t="n"/>
-      <c r="AU115" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV115" s="1" t="n"/>
+      <c r="AU115" s="1" t="n"/>
+      <c r="AV115" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW115" s="1" t="n"/>
+      <c r="AX115" s="1" t="n"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -18998,9 +19346,11 @@
         <v>0</v>
       </c>
       <c r="AN116" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO116" s="1" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="AO116" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP116" s="1" t="n"/>
       <c r="AQ116" s="1" t="n"/>
       <c r="AR116" s="1" t="n"/>
@@ -19009,6 +19359,7 @@
       <c r="AU116" s="1" t="n"/>
       <c r="AV116" s="1" t="n"/>
       <c r="AW116" s="1" t="n"/>
+      <c r="AX116" s="1" t="n"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -19182,6 +19533,9 @@
       <c r="AW117" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AX117" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -19355,6 +19709,9 @@
       <c r="AW118" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AX118" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -19499,25 +19856,28 @@
         <v>0</v>
       </c>
       <c r="AN119" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO119" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AO119" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP119" s="1" t="n"/>
+      <c r="AP119" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ119" s="1" t="n"/>
       <c r="AR119" s="1" t="n"/>
-      <c r="AS119" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS119" s="1" t="n"/>
       <c r="AT119" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU119" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV119" s="1" t="n"/>
+      <c r="AV119" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW119" s="1" t="n"/>
+      <c r="AX119" s="1" t="n"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -19662,9 +20022,11 @@
         <v>0</v>
       </c>
       <c r="AN120" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO120" s="1" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="AO120" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP120" s="1" t="n"/>
       <c r="AQ120" s="1" t="n"/>
       <c r="AR120" s="1" t="n"/>
@@ -19673,6 +20035,7 @@
       <c r="AU120" s="1" t="n"/>
       <c r="AV120" s="1" t="n"/>
       <c r="AW120" s="1" t="n"/>
+      <c r="AX120" s="1" t="n"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -19819,7 +20182,9 @@
       <c r="AN121" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AO121" s="1" t="n"/>
+      <c r="AO121" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP121" s="1" t="n"/>
       <c r="AQ121" s="1" t="n"/>
       <c r="AR121" s="1" t="n"/>
@@ -19828,6 +20193,7 @@
       <c r="AU121" s="1" t="n"/>
       <c r="AV121" s="1" t="n"/>
       <c r="AW121" s="1" t="n"/>
+      <c r="AX121" s="1" t="n"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -19974,7 +20340,9 @@
       <c r="AN122" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AO122" s="1" t="n"/>
+      <c r="AO122" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP122" s="1" t="n"/>
       <c r="AQ122" s="1" t="n"/>
       <c r="AR122" s="1" t="n"/>
@@ -19983,6 +20351,7 @@
       <c r="AU122" s="1" t="n"/>
       <c r="AV122" s="1" t="n"/>
       <c r="AW122" s="1" t="n"/>
+      <c r="AX122" s="1" t="n"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -20127,25 +20496,28 @@
         <v>0</v>
       </c>
       <c r="AN123" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO123" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP123" s="1" t="n"/>
+      <c r="AP123" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ123" s="1" t="n"/>
       <c r="AR123" s="1" t="n"/>
-      <c r="AS123" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS123" s="1" t="n"/>
       <c r="AT123" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU123" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV123" s="1" t="n"/>
+      <c r="AV123" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW123" s="1" t="n"/>
+      <c r="AX123" s="1" t="n"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -20290,11 +20662,11 @@
         <v>1</v>
       </c>
       <c r="AN124" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO124" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AO124" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="AP124" s="1" t="n">
         <v>1</v>
       </c>
@@ -20316,7 +20688,10 @@
       <c r="AV124" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AW124" s="1" t="n"/>
+      <c r="AW124" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX124" s="1" t="n"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -20421,9 +20796,11 @@
         <v>0</v>
       </c>
       <c r="AN125" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO125" s="1" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="AO125" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP125" s="1" t="n"/>
       <c r="AQ125" s="1" t="n"/>
       <c r="AR125" s="1" t="n"/>
@@ -20432,6 +20809,7 @@
       <c r="AU125" s="1" t="n"/>
       <c r="AV125" s="1" t="n"/>
       <c r="AW125" s="1" t="n"/>
+      <c r="AX125" s="1" t="n"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -20599,8 +20977,11 @@
       <c r="AU126" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV126" s="1" t="n"/>
+      <c r="AV126" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW126" s="1" t="n"/>
+      <c r="AX126" s="1" t="n"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -20745,25 +21126,28 @@
         <v>0</v>
       </c>
       <c r="AN127" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO127" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP127" s="1" t="n"/>
+      <c r="AP127" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ127" s="1" t="n"/>
       <c r="AR127" s="1" t="n"/>
-      <c r="AS127" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS127" s="1" t="n"/>
       <c r="AT127" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU127" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV127" s="1" t="n"/>
+      <c r="AV127" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW127" s="1" t="n"/>
+      <c r="AX127" s="1" t="n"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -20908,21 +21292,24 @@
         <v>0</v>
       </c>
       <c r="AN128" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO128" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP128" s="1" t="n"/>
+      <c r="AP128" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ128" s="1" t="n"/>
       <c r="AR128" s="1" t="n"/>
       <c r="AS128" s="1" t="n"/>
       <c r="AT128" s="1" t="n"/>
-      <c r="AU128" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV128" s="1" t="n"/>
+      <c r="AU128" s="1" t="n"/>
+      <c r="AV128" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW128" s="1" t="n"/>
+      <c r="AX128" s="1" t="n"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -21069,7 +21456,9 @@
       <c r="AN129" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AO129" s="1" t="n"/>
+      <c r="AO129" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP129" s="1" t="n"/>
       <c r="AQ129" s="1" t="n"/>
       <c r="AR129" s="1" t="n"/>
@@ -21078,6 +21467,7 @@
       <c r="AU129" s="1" t="n"/>
       <c r="AV129" s="1" t="n"/>
       <c r="AW129" s="1" t="n"/>
+      <c r="AX129" s="1" t="n"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -21224,7 +21614,9 @@
       <c r="AN130" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AO130" s="1" t="n"/>
+      <c r="AO130" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP130" s="1" t="n"/>
       <c r="AQ130" s="1" t="n"/>
       <c r="AR130" s="1" t="n"/>
@@ -21233,6 +21625,7 @@
       <c r="AU130" s="1" t="n"/>
       <c r="AV130" s="1" t="n"/>
       <c r="AW130" s="1" t="n"/>
+      <c r="AX130" s="1" t="n"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -21391,13 +21784,16 @@
       <c r="AR131" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AS131" s="1" t="n"/>
+      <c r="AS131" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AT131" s="1" t="n"/>
-      <c r="AU131" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV131" s="1" t="n"/>
+      <c r="AU131" s="1" t="n"/>
+      <c r="AV131" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW131" s="1" t="n"/>
+      <c r="AX131" s="1" t="n"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -21565,8 +21961,11 @@
       <c r="AU132" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV132" s="1" t="n"/>
+      <c r="AV132" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW132" s="1" t="n"/>
+      <c r="AX132" s="1" t="n"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -21711,25 +22110,28 @@
         <v>0</v>
       </c>
       <c r="AN133" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO133" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP133" s="1" t="n"/>
+      <c r="AP133" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ133" s="1" t="n"/>
       <c r="AR133" s="1" t="n"/>
-      <c r="AS133" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS133" s="1" t="n"/>
       <c r="AT133" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU133" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV133" s="1" t="n"/>
+      <c r="AV133" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW133" s="1" t="n"/>
+      <c r="AX133" s="1" t="n"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -21874,25 +22276,28 @@
         <v>0</v>
       </c>
       <c r="AN134" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO134" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP134" s="1" t="n"/>
+      <c r="AP134" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ134" s="1" t="n"/>
       <c r="AR134" s="1" t="n"/>
-      <c r="AS134" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS134" s="1" t="n"/>
       <c r="AT134" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU134" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV134" s="1" t="n"/>
+      <c r="AV134" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW134" s="1" t="n"/>
+      <c r="AX134" s="1" t="n"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -22037,21 +22442,24 @@
         <v>0</v>
       </c>
       <c r="AN135" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO135" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP135" s="1" t="n"/>
+      <c r="AP135" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ135" s="1" t="n"/>
       <c r="AR135" s="1" t="n"/>
       <c r="AS135" s="1" t="n"/>
       <c r="AT135" s="1" t="n"/>
-      <c r="AU135" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV135" s="1" t="n"/>
+      <c r="AU135" s="1" t="n"/>
+      <c r="AV135" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW135" s="1" t="n"/>
+      <c r="AX135" s="1" t="n"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -22196,25 +22604,28 @@
         <v>0</v>
       </c>
       <c r="AN136" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO136" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP136" s="1" t="n"/>
+      <c r="AP136" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ136" s="1" t="n"/>
       <c r="AR136" s="1" t="n"/>
-      <c r="AS136" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS136" s="1" t="n"/>
       <c r="AT136" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU136" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV136" s="1" t="n"/>
+      <c r="AV136" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW136" s="1" t="n"/>
+      <c r="AX136" s="1" t="n"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -22359,25 +22770,28 @@
         <v>0</v>
       </c>
       <c r="AN137" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO137" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP137" s="1" t="n"/>
+      <c r="AP137" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ137" s="1" t="n"/>
       <c r="AR137" s="1" t="n"/>
-      <c r="AS137" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS137" s="1" t="n"/>
       <c r="AT137" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU137" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV137" s="1" t="n"/>
+      <c r="AV137" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW137" s="1" t="n"/>
+      <c r="AX137" s="1" t="n"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -22522,25 +22936,28 @@
         <v>0</v>
       </c>
       <c r="AN138" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO138" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP138" s="1" t="n"/>
+      <c r="AP138" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ138" s="1" t="n"/>
       <c r="AR138" s="1" t="n"/>
-      <c r="AS138" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS138" s="1" t="n"/>
       <c r="AT138" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU138" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV138" s="1" t="n"/>
+      <c r="AV138" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW138" s="1" t="n"/>
+      <c r="AX138" s="1" t="n"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -22687,7 +23104,9 @@
       <c r="AN139" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AO139" s="1" t="n"/>
+      <c r="AO139" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP139" s="1" t="n"/>
       <c r="AQ139" s="1" t="n"/>
       <c r="AR139" s="1" t="n"/>
@@ -22696,6 +23115,7 @@
       <c r="AU139" s="1" t="n"/>
       <c r="AV139" s="1" t="n"/>
       <c r="AW139" s="1" t="n"/>
+      <c r="AX139" s="1" t="n"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -22800,9 +23220,11 @@
         <v>0</v>
       </c>
       <c r="AN140" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO140" s="1" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="AO140" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP140" s="1" t="n"/>
       <c r="AQ140" s="1" t="n"/>
       <c r="AR140" s="1" t="n"/>
@@ -22811,6 +23233,7 @@
       <c r="AU140" s="1" t="n"/>
       <c r="AV140" s="1" t="n"/>
       <c r="AW140" s="1" t="n"/>
+      <c r="AX140" s="1" t="n"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -22969,11 +23392,14 @@
       <c r="AR141" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AS141" s="1" t="n"/>
+      <c r="AS141" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AT141" s="1" t="n"/>
       <c r="AU141" s="1" t="n"/>
       <c r="AV141" s="1" t="n"/>
       <c r="AW141" s="1" t="n"/>
+      <c r="AX141" s="1" t="n"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -23141,8 +23567,11 @@
       <c r="AU142" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV142" s="1" t="n"/>
+      <c r="AV142" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW142" s="1" t="n"/>
+      <c r="AX142" s="1" t="n"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -23287,25 +23716,28 @@
         <v>0</v>
       </c>
       <c r="AN143" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO143" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP143" s="1" t="n"/>
+      <c r="AP143" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ143" s="1" t="n"/>
       <c r="AR143" s="1" t="n"/>
-      <c r="AS143" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS143" s="1" t="n"/>
       <c r="AT143" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU143" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV143" s="1" t="n"/>
+      <c r="AV143" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW143" s="1" t="n"/>
+      <c r="AX143" s="1" t="n"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -23450,25 +23882,28 @@
         <v>0</v>
       </c>
       <c r="AN144" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO144" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP144" s="1" t="n"/>
+      <c r="AP144" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ144" s="1" t="n"/>
       <c r="AR144" s="1" t="n"/>
-      <c r="AS144" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS144" s="1" t="n"/>
       <c r="AT144" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU144" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV144" s="1" t="n"/>
+      <c r="AV144" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW144" s="1" t="n"/>
+      <c r="AX144" s="1" t="n"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -23613,25 +24048,28 @@
         <v>0</v>
       </c>
       <c r="AN145" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO145" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP145" s="1" t="n"/>
+      <c r="AP145" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ145" s="1" t="n"/>
       <c r="AR145" s="1" t="n"/>
-      <c r="AS145" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS145" s="1" t="n"/>
       <c r="AT145" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU145" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV145" s="1" t="n"/>
+      <c r="AV145" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW145" s="1" t="n"/>
+      <c r="AX145" s="1" t="n"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -23776,11 +24214,11 @@
         <v>1</v>
       </c>
       <c r="AN146" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO146" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AO146" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="AP146" s="1" t="n">
         <v>1</v>
       </c>
@@ -23799,8 +24237,11 @@
       <c r="AU146" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV146" s="1" t="n"/>
+      <c r="AV146" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW146" s="1" t="n"/>
+      <c r="AX146" s="1" t="n"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -23945,9 +24386,11 @@
         <v>0</v>
       </c>
       <c r="AN147" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO147" s="1" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="AO147" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP147" s="1" t="n"/>
       <c r="AQ147" s="1" t="n"/>
       <c r="AR147" s="1" t="n"/>
@@ -23956,6 +24399,7 @@
       <c r="AU147" s="1" t="n"/>
       <c r="AV147" s="1" t="n"/>
       <c r="AW147" s="1" t="n"/>
+      <c r="AX147" s="1" t="n"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -24102,7 +24546,9 @@
       <c r="AN148" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AO148" s="1" t="n"/>
+      <c r="AO148" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP148" s="1" t="n"/>
       <c r="AQ148" s="1" t="n"/>
       <c r="AR148" s="1" t="n"/>
@@ -24111,6 +24557,7 @@
       <c r="AU148" s="1" t="n"/>
       <c r="AV148" s="1" t="n"/>
       <c r="AW148" s="1" t="n"/>
+      <c r="AX148" s="1" t="n"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -24257,11 +24704,14 @@
       <c r="AR149" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AS149" s="1" t="n"/>
+      <c r="AS149" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AT149" s="1" t="n"/>
       <c r="AU149" s="1" t="n"/>
       <c r="AV149" s="1" t="n"/>
       <c r="AW149" s="1" t="n"/>
+      <c r="AX149" s="1" t="n"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -24420,13 +24870,16 @@
       <c r="AR150" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AS150" s="1" t="n"/>
+      <c r="AS150" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AT150" s="1" t="n"/>
-      <c r="AU150" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV150" s="1" t="n"/>
+      <c r="AU150" s="1" t="n"/>
+      <c r="AV150" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW150" s="1" t="n"/>
+      <c r="AX150" s="1" t="n"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -24571,25 +25024,28 @@
         <v>0</v>
       </c>
       <c r="AN151" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO151" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP151" s="1" t="n"/>
+      <c r="AP151" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ151" s="1" t="n"/>
       <c r="AR151" s="1" t="n"/>
-      <c r="AS151" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS151" s="1" t="n"/>
       <c r="AT151" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU151" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV151" s="1" t="n"/>
+      <c r="AV151" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW151" s="1" t="n"/>
+      <c r="AX151" s="1" t="n"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -24734,9 +25190,11 @@
         <v>0</v>
       </c>
       <c r="AN152" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO152" s="1" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="AO152" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP152" s="1" t="n"/>
       <c r="AQ152" s="1" t="n"/>
       <c r="AR152" s="1" t="n"/>
@@ -24745,6 +25203,7 @@
       <c r="AU152" s="1" t="n"/>
       <c r="AV152" s="1" t="n"/>
       <c r="AW152" s="1" t="n"/>
+      <c r="AX152" s="1" t="n"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -24891,7 +25350,9 @@
       <c r="AN153" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AO153" s="1" t="n"/>
+      <c r="AO153" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP153" s="1" t="n"/>
       <c r="AQ153" s="1" t="n"/>
       <c r="AR153" s="1" t="n"/>
@@ -24900,6 +25361,7 @@
       <c r="AU153" s="1" t="n"/>
       <c r="AV153" s="1" t="n"/>
       <c r="AW153" s="1" t="n"/>
+      <c r="AX153" s="1" t="n"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -25044,11 +25506,11 @@
         <v>1</v>
       </c>
       <c r="AN154" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO154" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AO154" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="AP154" s="1" t="n">
         <v>1</v>
       </c>
@@ -25067,8 +25529,11 @@
       <c r="AU154" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV154" s="1" t="n"/>
+      <c r="AV154" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW154" s="1" t="n"/>
+      <c r="AX154" s="1" t="n"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -25213,21 +25678,24 @@
         <v>0</v>
       </c>
       <c r="AN155" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO155" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP155" s="1" t="n"/>
+      <c r="AP155" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ155" s="1" t="n"/>
       <c r="AR155" s="1" t="n"/>
       <c r="AS155" s="1" t="n"/>
       <c r="AT155" s="1" t="n"/>
-      <c r="AU155" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV155" s="1" t="n"/>
+      <c r="AU155" s="1" t="n"/>
+      <c r="AV155" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW155" s="1" t="n"/>
+      <c r="AX155" s="1" t="n"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -25332,9 +25800,11 @@
         <v>0</v>
       </c>
       <c r="AN156" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO156" s="1" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="AO156" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP156" s="1" t="n"/>
       <c r="AQ156" s="1" t="n"/>
       <c r="AR156" s="1" t="n"/>
@@ -25343,6 +25813,7 @@
       <c r="AU156" s="1" t="n"/>
       <c r="AV156" s="1" t="n"/>
       <c r="AW156" s="1" t="n"/>
+      <c r="AX156" s="1" t="n"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -25510,8 +25981,11 @@
       <c r="AU157" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV157" s="1" t="n"/>
+      <c r="AV157" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW157" s="1" t="n"/>
+      <c r="AX157" s="1" t="n"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -25656,9 +26130,11 @@
         <v>0</v>
       </c>
       <c r="AN158" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO158" s="1" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="AO158" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP158" s="1" t="n"/>
       <c r="AQ158" s="1" t="n"/>
       <c r="AR158" s="1" t="n"/>
@@ -25667,6 +26143,7 @@
       <c r="AU158" s="1" t="n"/>
       <c r="AV158" s="1" t="n"/>
       <c r="AW158" s="1" t="n"/>
+      <c r="AX158" s="1" t="n"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -25811,25 +26288,28 @@
         <v>0</v>
       </c>
       <c r="AN159" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO159" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP159" s="1" t="n"/>
+      <c r="AP159" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ159" s="1" t="n"/>
       <c r="AR159" s="1" t="n"/>
-      <c r="AS159" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS159" s="1" t="n"/>
       <c r="AT159" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU159" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV159" s="1" t="n"/>
+      <c r="AV159" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW159" s="1" t="n"/>
+      <c r="AX159" s="1" t="n"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -26003,6 +26483,9 @@
       <c r="AW160" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AX160" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -26170,8 +26653,11 @@
       <c r="AU161" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV161" s="1" t="n"/>
+      <c r="AV161" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW161" s="1" t="n"/>
+      <c r="AX161" s="1" t="n"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -26316,9 +26802,11 @@
         <v>0</v>
       </c>
       <c r="AN162" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO162" s="1" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="AO162" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP162" s="1" t="n"/>
       <c r="AQ162" s="1" t="n"/>
       <c r="AR162" s="1" t="n"/>
@@ -26327,6 +26815,7 @@
       <c r="AU162" s="1" t="n"/>
       <c r="AV162" s="1" t="n"/>
       <c r="AW162" s="1" t="n"/>
+      <c r="AX162" s="1" t="n"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -26485,15 +26974,18 @@
       <c r="AR163" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AS163" s="1" t="n"/>
+      <c r="AS163" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AT163" s="1" t="n"/>
-      <c r="AU163" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AU163" s="1" t="n"/>
       <c r="AV163" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AW163" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX163" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -26640,21 +27132,24 @@
         <v>0</v>
       </c>
       <c r="AN164" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO164" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP164" s="1" t="n"/>
+      <c r="AP164" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ164" s="1" t="n"/>
       <c r="AR164" s="1" t="n"/>
       <c r="AS164" s="1" t="n"/>
       <c r="AT164" s="1" t="n"/>
-      <c r="AU164" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV164" s="1" t="n"/>
+      <c r="AU164" s="1" t="n"/>
+      <c r="AV164" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW164" s="1" t="n"/>
+      <c r="AX164" s="1" t="n"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -26799,25 +27294,28 @@
         <v>0</v>
       </c>
       <c r="AN165" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO165" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP165" s="1" t="n"/>
+      <c r="AP165" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ165" s="1" t="n"/>
       <c r="AR165" s="1" t="n"/>
-      <c r="AS165" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS165" s="1" t="n"/>
       <c r="AT165" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU165" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV165" s="1" t="n"/>
+      <c r="AV165" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW165" s="1" t="n"/>
+      <c r="AX165" s="1" t="n"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -26950,9 +27448,11 @@
         <v>0</v>
       </c>
       <c r="AN166" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO166" s="1" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="AO166" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP166" s="1" t="n"/>
       <c r="AQ166" s="1" t="n"/>
       <c r="AR166" s="1" t="n"/>
@@ -26961,6 +27461,7 @@
       <c r="AU166" s="1" t="n"/>
       <c r="AV166" s="1" t="n"/>
       <c r="AW166" s="1" t="n"/>
+      <c r="AX166" s="1" t="n"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -27134,6 +27635,9 @@
       <c r="AW167" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AX167" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -27292,11 +27796,14 @@
       <c r="AR168" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AS168" s="1" t="n"/>
+      <c r="AS168" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AT168" s="1" t="n"/>
       <c r="AU168" s="1" t="n"/>
       <c r="AV168" s="1" t="n"/>
       <c r="AW168" s="1" t="n"/>
+      <c r="AX168" s="1" t="n"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -27441,9 +27948,11 @@
         <v>0</v>
       </c>
       <c r="AN169" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO169" s="1" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="AO169" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP169" s="1" t="n"/>
       <c r="AQ169" s="1" t="n"/>
       <c r="AR169" s="1" t="n"/>
@@ -27452,6 +27961,7 @@
       <c r="AU169" s="1" t="n"/>
       <c r="AV169" s="1" t="n"/>
       <c r="AW169" s="1" t="n"/>
+      <c r="AX169" s="1" t="n"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -27610,13 +28120,16 @@
       <c r="AR170" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AS170" s="1" t="n"/>
+      <c r="AS170" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AT170" s="1" t="n"/>
-      <c r="AU170" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV170" s="1" t="n"/>
+      <c r="AU170" s="1" t="n"/>
+      <c r="AV170" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW170" s="1" t="n"/>
+      <c r="AX170" s="1" t="n"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -27761,11 +28274,11 @@
         <v>1</v>
       </c>
       <c r="AN171" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO171" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AO171" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="AP171" s="1" t="n">
         <v>1</v>
       </c>
@@ -27784,8 +28297,11 @@
       <c r="AU171" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV171" s="1" t="n"/>
+      <c r="AV171" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW171" s="1" t="n"/>
+      <c r="AX171" s="1" t="n"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -27890,9 +28406,11 @@
         <v>0</v>
       </c>
       <c r="AN172" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO172" s="1" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="AO172" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AP172" s="1" t="n"/>
       <c r="AQ172" s="1" t="n"/>
       <c r="AR172" s="1" t="n"/>
@@ -27901,6 +28419,7 @@
       <c r="AU172" s="1" t="n"/>
       <c r="AV172" s="1" t="n"/>
       <c r="AW172" s="1" t="n"/>
+      <c r="AX172" s="1" t="n"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -28059,13 +28578,16 @@
       <c r="AR173" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AS173" s="1" t="n"/>
+      <c r="AS173" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AT173" s="1" t="n"/>
-      <c r="AU173" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV173" s="1" t="n"/>
+      <c r="AU173" s="1" t="n"/>
+      <c r="AV173" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW173" s="1" t="n"/>
+      <c r="AX173" s="1" t="n"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -28210,21 +28732,24 @@
         <v>0</v>
       </c>
       <c r="AN174" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO174" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP174" s="1" t="n"/>
+      <c r="AP174" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ174" s="1" t="n"/>
       <c r="AR174" s="1" t="n"/>
       <c r="AS174" s="1" t="n"/>
       <c r="AT174" s="1" t="n"/>
-      <c r="AU174" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV174" s="1" t="n"/>
+      <c r="AU174" s="1" t="n"/>
+      <c r="AV174" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW174" s="1" t="n"/>
+      <c r="AX174" s="1" t="n"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -28369,21 +28894,24 @@
         <v>0</v>
       </c>
       <c r="AN175" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO175" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP175" s="1" t="n"/>
+      <c r="AP175" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ175" s="1" t="n"/>
       <c r="AR175" s="1" t="n"/>
       <c r="AS175" s="1" t="n"/>
       <c r="AT175" s="1" t="n"/>
-      <c r="AU175" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV175" s="1" t="n"/>
+      <c r="AU175" s="1" t="n"/>
+      <c r="AV175" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW175" s="1" t="n"/>
+      <c r="AX175" s="1" t="n"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -28542,13 +29070,16 @@
       <c r="AR176" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AS176" s="1" t="n"/>
+      <c r="AS176" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AT176" s="1" t="n"/>
-      <c r="AU176" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV176" s="1" t="n"/>
+      <c r="AU176" s="1" t="n"/>
+      <c r="AV176" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW176" s="1" t="n"/>
+      <c r="AX176" s="1" t="n"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -28693,25 +29224,28 @@
         <v>0</v>
       </c>
       <c r="AN177" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO177" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AP177" s="1" t="n"/>
+      <c r="AP177" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ177" s="1" t="n"/>
       <c r="AR177" s="1" t="n"/>
-      <c r="AS177" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS177" s="1" t="n"/>
       <c r="AT177" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU177" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV177" s="1" t="n"/>
+      <c r="AV177" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW177" s="1" t="n"/>
+      <c r="AX177" s="1" t="n"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -28885,6 +29419,9 @@
       <c r="AW178" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AX178" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -29043,13 +29580,16 @@
       <c r="AR179" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AS179" s="1" t="n"/>
+      <c r="AS179" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AT179" s="1" t="n"/>
-      <c r="AU179" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV179" s="1" t="n"/>
+      <c r="AU179" s="1" t="n"/>
+      <c r="AV179" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW179" s="1" t="n"/>
+      <c r="AX179" s="1" t="n"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -29132,19 +29672,20 @@
       <c r="AL180" s="1" t="n"/>
       <c r="AM180" s="1" t="n"/>
       <c r="AN180" s="1" t="n"/>
-      <c r="AO180" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP180" s="1" t="n"/>
+      <c r="AO180" s="1" t="n"/>
+      <c r="AP180" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ180" s="1" t="n"/>
       <c r="AR180" s="1" t="n"/>
       <c r="AS180" s="1" t="n"/>
       <c r="AT180" s="1" t="n"/>
-      <c r="AU180" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV180" s="1" t="n"/>
+      <c r="AU180" s="1" t="n"/>
+      <c r="AV180" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AW180" s="1" t="n"/>
+      <c r="AX180" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
